--- a/docs/4G_LTE_Mobility_Management/Connected_Mode_eRAN21.1_Feature_Sheets.xlsx
+++ b/docs/4G_LTE_Mobility_Management/Connected_Mode_eRAN21.1_Feature_Sheets.xlsx
@@ -43,7 +43,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,7 +131,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="000070C0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -139,6 +139,12 @@
       <b val="1"/>
       <color rgb="002E75B6"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -284,11 +290,11 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -298,14 +304,14 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -678,16 +684,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -702,6 +710,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -771,10 +781,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    •  Parameter list: Value column holds only the value. Comments sit in the Comment column.</t>
+          <t xml:space="preserve">    •  Parameter list: Value = value only (blue). Comment = how to use it. Parameter Meaning = what it is. Reference = Feature ID + document name.</t>
         </is>
       </c>
     </row>
@@ -1177,34 +1187,34 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="E22:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" location="'03 Overview'!A1" display="03 Overview →"/>
@@ -1223,7 +1233,7 @@
     <hyperlink ref="E31" location="'14 GERAN Multi-PLMN'!A1" display="Open sheet →"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  Contents&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -1242,16 +1252,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1266,6 +1278,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1349,6 +1363,8 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="110" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -1367,6 +1383,8 @@
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
@@ -1381,6 +1399,8 @@
       <c r="E18" s="29" t="n"/>
       <c r="F18" s="29" t="n"/>
       <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
     </row>
     <row r="19" ht="110" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
@@ -1398,6 +1418,8 @@
       <c r="E19" s="29" t="n"/>
       <c r="F19" s="29" t="n"/>
       <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
     </row>
     <row r="20" ht="6" customHeight="1"/>
     <row r="21" ht="18" customHeight="1">
@@ -1412,6 +1434,8 @@
       <c r="E21" s="32" t="n"/>
       <c r="F21" s="32" t="n"/>
       <c r="G21" s="32" t="n"/>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="32" t="n"/>
     </row>
     <row r="22" ht="110" customHeight="1">
       <c r="A22" s="33" t="inlineStr">
@@ -1429,6 +1453,8 @@
       <c r="E22" s="32" t="n"/>
       <c r="F22" s="32" t="n"/>
       <c r="G22" s="32" t="n"/>
+      <c r="H22" s="32" t="n"/>
+      <c r="I22" s="32" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
@@ -1446,6 +1472,8 @@
       <c r="E23" s="25" t="n"/>
       <c r="F23" s="25" t="n"/>
       <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -1463,6 +1491,8 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="25" t="n"/>
       <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
@@ -1480,6 +1510,8 @@
       <c r="E25" s="25" t="n"/>
       <c r="F25" s="25" t="n"/>
       <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="26" t="inlineStr"/>
@@ -1493,6 +1525,8 @@
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="25" t="n"/>
       <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="14" customHeight="1"/>
     <row r="28" ht="24" customHeight="1">
@@ -1519,7 +1553,7 @@
       </c>
     </row>
     <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -1555,8 +1589,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
       <c r="A35" s="17" t="n">
         <v>1</v>
       </c>
@@ -1590,8 +1634,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>Enables frequency-priority-based inter-frequency handover (measurement-based).</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
       <c r="A36" s="17" t="n">
         <v>2</v>
       </c>
@@ -1625,8 +1679,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>When MLB is triggered, FreqPri yields so load movement is owned by Intra-RAT MLB.</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11 / Table 11-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
       <c r="A37" s="17" t="n">
         <v>3</v>
       </c>
@@ -1660,8 +1724,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>Uses FreqPri A2 (serving poor) as a FreqPri start/stop condition. Deselect in same-coverage multi-band.</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
       <c r="A38" s="17" t="n">
         <v>4</v>
       </c>
@@ -1695,8 +1769,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>Enables frequency-priority blind handover in multi-band same-coverage.</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 10-6 / §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
       <c r="A39" s="17" t="n">
         <v>5</v>
       </c>
@@ -1730,8 +1814,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>Adds load, overlap and PCI checks before a frequency-priority HO is started.</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
       <c r="A40" s="17" t="n">
         <v>6</v>
       </c>
@@ -1765,8 +1859,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Whether this neighbouring frequency is a measurement object for frequency-priority HO.</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
       <c r="A41" s="17" t="n">
         <v>7</v>
       </c>
@@ -1800,8 +1904,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>Priority of this frequency among frequency-priority measurement objects. Higher value = preferred.</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
       <c r="A42" s="17" t="n">
         <v>8</v>
       </c>
@@ -1835,8 +1949,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>Event A1 RSRP threshold that indicates serving is good enough to start or keep FreqPri.</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
       <c r="A43" s="17" t="n">
         <v>9</v>
       </c>
@@ -1870,8 +1994,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>Event A2 RSRP threshold used when A2-based frequency-priority mode is enabled.</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
       <c r="A44" s="17" t="n">
         <v>10</v>
       </c>
@@ -1905,8 +2039,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>A4 RSRP threshold of the high-priority (usually high-band) target. May add FreqPriHoA4ThldRsrpOffset per EARFCN.</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
       <c r="A45" s="17" t="n">
         <v>11</v>
       </c>
@@ -1940,8 +2084,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>TimeToTrig for A4. 5120 ms disables frequency-priority IFHO.</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-9 / §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
       <c r="A46" s="17" t="n">
         <v>12</v>
       </c>
@@ -1975,8 +2129,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>Quantity used to trigger FreqPri event A1. RSRP is recommended.</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
       <c r="A47" s="17" t="n">
         <v>13</v>
       </c>
@@ -2010,8 +2174,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>Time the eNodeB waits for a frequency-priority A4 measurement report.</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
       <c r="A48" s="17" t="n">
         <v>14</v>
       </c>
@@ -2045,8 +2219,18 @@
           <t>11</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>Protects a UE after an incoming unnecessary HO so FreqPri does not bounce it back immediately.</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
       <c r="A49" s="17" t="n">
         <v>15</v>
       </c>
@@ -2080,33 +2264,43 @@
           <t>11</t>
         </is>
       </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>Priority used to pick a preferred neighbouring cell for frequency-priority blind HO.</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="D26:I26"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -2115,7 +2309,7 @@
     <hyperlink ref="D4" location="'04 Basic Functions'!A1" display="Ch.4 Basic (must)"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  11 Frequency-Priority-based Inter-Frequency Handover&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -2134,16 +2328,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2158,6 +2354,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -2241,6 +2439,8 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="98" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -2257,6 +2457,8 @@
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
@@ -2271,6 +2473,8 @@
       <c r="E18" s="29" t="n"/>
       <c r="F18" s="29" t="n"/>
       <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
     </row>
     <row r="19" ht="98" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
@@ -2286,6 +2490,8 @@
       <c r="E19" s="29" t="n"/>
       <c r="F19" s="29" t="n"/>
       <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
@@ -2303,6 +2509,8 @@
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="25" t="n"/>
       <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -2320,6 +2528,8 @@
       <c r="E21" s="25" t="n"/>
       <c r="F21" s="25" t="n"/>
       <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -2337,6 +2547,8 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="25" t="n"/>
       <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="26" t="inlineStr"/>
@@ -2350,6 +2562,8 @@
       <c r="E23" s="25" t="n"/>
       <c r="F23" s="25" t="n"/>
       <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="26" t="inlineStr"/>
@@ -2363,6 +2577,8 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="25" t="n"/>
       <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="6" customHeight="1"/>
     <row r="26" ht="18" customHeight="1">
@@ -2377,6 +2593,8 @@
       <c r="E26" s="32" t="n"/>
       <c r="F26" s="32" t="n"/>
       <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="33" t="inlineStr">
@@ -2390,6 +2608,8 @@
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
     </row>
     <row r="28" ht="14" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
@@ -2416,7 +2636,7 @@
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -2452,8 +2672,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
       <c r="A36" s="17" t="n">
         <v>1</v>
       </c>
@@ -2487,8 +2717,18 @@
           <t>→ Ch.5.3</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>Coverage-based inter-frequency HO must be on before speed-based IFHO can be enabled.</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.3 / §12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
       <c r="A37" s="17" t="n">
         <v>2</v>
       </c>
@@ -2522,8 +2762,18 @@
           <t>12</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>Enables speed-based inter-frequency handover (FDD). High-speed UEs are steered to the coverage layer.</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
       <c r="A38" s="17" t="n">
         <v>3</v>
       </c>
@@ -2557,8 +2807,18 @@
           <t>12</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>Speed-based HO does not have its own A2 family; it re-uses coverage inter-frequency A2/A3/A4/A5.</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
       <c r="A39" s="17" t="n">
         <v>4</v>
       </c>
@@ -2592,35 +2852,45 @@
           <t>→ Ch.4</t>
         </is>
       </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>The coverage-layer frequency must be a connected-mode measurement object.</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4 / §12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="D20:G20"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="D20:I20"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -2631,7 +2901,7 @@
     <hyperlink ref="G39" location="'04 Basic Functions'!A1" display="→ Ch.4"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  12 Speed-based Inter-Frequency Handover (FDD)&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -2650,16 +2920,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2674,6 +2946,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -2792,6 +3066,8 @@
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -2805,6 +3081,8 @@
       <c r="E21" s="14" t="n"/>
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
@@ -2822,6 +3100,8 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="25" t="n"/>
       <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -2839,6 +3119,8 @@
       <c r="E23" s="25" t="n"/>
       <c r="F23" s="25" t="n"/>
       <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -2856,6 +3138,8 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="25" t="n"/>
       <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="26" t="inlineStr"/>
@@ -2869,6 +3153,8 @@
       <c r="E25" s="25" t="n"/>
       <c r="F25" s="25" t="n"/>
       <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="6" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
@@ -2883,6 +3169,8 @@
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="33" t="inlineStr">
@@ -2896,6 +3184,8 @@
       <c r="E28" s="32" t="n"/>
       <c r="F28" s="32" t="n"/>
       <c r="G28" s="32" t="n"/>
+      <c r="H28" s="32" t="n"/>
+      <c r="I28" s="32" t="n"/>
     </row>
     <row r="29" ht="14" customHeight="1"/>
     <row r="30" ht="24" customHeight="1">
@@ -2922,7 +3212,7 @@
       </c>
     </row>
     <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -2958,8 +3248,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
       <c r="A37" s="17" t="n">
         <v>1</v>
       </c>
@@ -2993,8 +3293,18 @@
           <t>13</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>Enables separate UTRAN mobility policies per PLMN / RNC at target-decision time.</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-070216  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
       <c r="A38" s="17" t="n">
         <v>2</v>
       </c>
@@ -3028,8 +3338,18 @@
           <t>13</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>Identifies the UTRAN RNC (PLMN + RNC ID) whose capabilities are configured.</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-070216  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 11-1 / §13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
       <c r="A39" s="17" t="n">
         <v>3</v>
       </c>
@@ -3063,8 +3383,18 @@
           <t>13</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>Whether that RNC supports PS handover. If off, the eNodeB will not choose PS HO toward it.</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-070216  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §13.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
       <c r="A40" s="17" t="n">
         <v>4</v>
       </c>
@@ -3098,8 +3428,18 @@
           <t>13</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Whether VoIP services can be handed over to that UTRAN RNC.</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-070216  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §13.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
       <c r="A41" s="17" t="n">
         <v>5</v>
       </c>
@@ -3133,8 +3473,18 @@
           <t>13</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>Whether SRVCC to that UTRAN RNC is supported.</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-070216  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §13.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
       <c r="A42" s="17" t="n">
         <v>6</v>
       </c>
@@ -3168,8 +3518,18 @@
           <t>13</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>Whether that RNC supports CN-based RIM for SI acquisition (CSFB / redirect method).</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-070216  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §13.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
       <c r="A43" s="17" t="n">
         <v>7</v>
       </c>
@@ -3203,8 +3563,18 @@
           <t>13</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>Whether that RNC supports ultra-flash CSFB from E-UTRAN.</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-070216  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §13.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
       <c r="A44" s="17" t="n">
         <v>8</v>
       </c>
@@ -3238,36 +3608,46 @@
           <t>→ Ch.5.4</t>
         </is>
       </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>Coverage IRAT to UTRAN must already be enabled; this chapter only specialises the policy per PLMN.</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001019  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.4 / §13</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A14:I14"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A34:I34"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -3277,7 +3657,7 @@
     <hyperlink ref="G44" location="'05 Coverage HO'!A1" display="→ Ch.5.4"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  13 Separate Mobility Policies to UTRAN for Multi PLMN (FDD)&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -3296,16 +3676,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3320,6 +3702,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -3399,6 +3783,8 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -3412,6 +3798,8 @@
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
@@ -3429,6 +3817,8 @@
       <c r="E17" s="25" t="n"/>
       <c r="F17" s="25" t="n"/>
       <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -3446,6 +3836,8 @@
       <c r="E18" s="25" t="n"/>
       <c r="F18" s="25" t="n"/>
       <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -3463,6 +3855,8 @@
       <c r="E19" s="25" t="n"/>
       <c r="F19" s="25" t="n"/>
       <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="26" t="inlineStr"/>
@@ -3476,6 +3870,8 @@
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="25" t="n"/>
       <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="18" customHeight="1">
@@ -3490,6 +3886,8 @@
       <c r="E22" s="32" t="n"/>
       <c r="F22" s="32" t="n"/>
       <c r="G22" s="32" t="n"/>
+      <c r="H22" s="32" t="n"/>
+      <c r="I22" s="32" t="n"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="33" t="inlineStr">
@@ -3503,6 +3901,8 @@
       <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
       <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
     </row>
     <row r="24" ht="14" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
@@ -3529,7 +3929,7 @@
       </c>
     </row>
     <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -3565,8 +3965,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
       <c r="A32" s="17" t="n">
         <v>1</v>
       </c>
@@ -3600,8 +4010,18 @@
           <t>14</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>Enables separate GERAN mobility policies per PLMN / BSC at target-decision time.</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-111204  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
       <c r="A33" s="17" t="n">
         <v>2</v>
       </c>
@@ -3635,8 +4055,18 @@
           <t>14</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>Identifies the GERAN BSC (PLMN + BSC ID) whose capabilities are configured.</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-111204  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
       <c r="A34" s="17" t="n">
         <v>3</v>
       </c>
@@ -3670,8 +4100,18 @@
           <t>14</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>GERAN HO, CCO and SI-by-RIM capabilities of that BSC. Confirm option names in MAE.</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-111204  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
       <c r="A35" s="17" t="n">
         <v>4</v>
       </c>
@@ -3705,31 +4145,41 @@
           <t>→ Ch.5.5</t>
         </is>
       </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>Coverage IRAT to GERAN must already be enabled; this chapter only specialises the policy per PLMN.</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001020  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.5 / §14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="D17:I17"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="D18:I18"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -3738,7 +4188,7 @@
     <hyperlink ref="G35" location="'05 Coverage HO'!A1" display="→ Ch.5.5"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  14 Separate Mobility Policies to GERAN for Multi PLMN&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -3757,16 +4207,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3781,6 +4233,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -3864,6 +4318,8 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -3877,6 +4333,8 @@
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1"/>
     <row r="18" ht="24" customHeight="1">
@@ -3982,7 +4440,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -4018,8 +4476,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
       <c r="A38" s="17" t="n">
         <v>1</v>
       </c>
@@ -4053,32 +4521,42 @@
           <t>Overview</t>
         </is>
       </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>Chapter 3 has no activation parameter.</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>—  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §3 Overview</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -4088,7 +4566,7 @@
     <hyperlink ref="G38" location="'04 Basic Functions'!A1" display="Overview"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  3 Overview of Mobility Management in Connected Mode&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -4107,16 +4585,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4131,6 +4611,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -4265,6 +4747,8 @@
       <c r="E23" s="14" t="n"/>
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24" ht="110" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
@@ -4281,6 +4765,8 @@
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="10" customHeight="1"/>
     <row r="26" ht="22" customHeight="1">
@@ -4314,6 +4800,8 @@
       <c r="E29" s="25" t="n"/>
       <c r="F29" s="25" t="n"/>
       <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -4331,6 +4819,8 @@
       <c r="E30" s="25" t="n"/>
       <c r="F30" s="25" t="n"/>
       <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -4348,6 +4838,8 @@
       <c r="E31" s="25" t="n"/>
       <c r="F31" s="25" t="n"/>
       <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
     </row>
     <row r="32" ht="10" customHeight="1"/>
     <row r="33" ht="22" customHeight="1">
@@ -4378,6 +4870,8 @@
       <c r="E37" s="29" t="n"/>
       <c r="F37" s="29" t="n"/>
       <c r="G37" s="29" t="n"/>
+      <c r="H37" s="29" t="n"/>
+      <c r="I37" s="29" t="n"/>
     </row>
     <row r="38" ht="110" customHeight="1">
       <c r="A38" s="30" t="inlineStr">
@@ -4399,6 +4893,8 @@
       <c r="E38" s="29" t="n"/>
       <c r="F38" s="29" t="n"/>
       <c r="G38" s="29" t="n"/>
+      <c r="H38" s="29" t="n"/>
+      <c r="I38" s="29" t="n"/>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
@@ -4436,6 +4932,8 @@
       <c r="E45" s="32" t="n"/>
       <c r="F45" s="32" t="n"/>
       <c r="G45" s="32" t="n"/>
+      <c r="H45" s="32" t="n"/>
+      <c r="I45" s="32" t="n"/>
     </row>
     <row r="46" ht="98" customHeight="1">
       <c r="A46" s="33" t="inlineStr">
@@ -4451,6 +4949,8 @@
       <c r="E46" s="32" t="n"/>
       <c r="F46" s="32" t="n"/>
       <c r="G46" s="32" t="n"/>
+      <c r="H46" s="32" t="n"/>
+      <c r="I46" s="32" t="n"/>
     </row>
     <row r="47" ht="10" customHeight="1"/>
     <row r="48" ht="22" customHeight="1">
@@ -4484,6 +4984,8 @@
       <c r="E51" s="25" t="n"/>
       <c r="F51" s="25" t="n"/>
       <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
@@ -4501,6 +5003,8 @@
       <c r="E52" s="25" t="n"/>
       <c r="F52" s="25" t="n"/>
       <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
+      <c r="I52" s="25" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="26" t="inlineStr">
@@ -4518,6 +5022,8 @@
       <c r="E53" s="25" t="n"/>
       <c r="F53" s="25" t="n"/>
       <c r="G53" s="25" t="n"/>
+      <c r="H53" s="25" t="n"/>
+      <c r="I53" s="25" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="26" t="inlineStr"/>
@@ -4531,6 +5037,8 @@
       <c r="E54" s="25" t="n"/>
       <c r="F54" s="25" t="n"/>
       <c r="G54" s="25" t="n"/>
+      <c r="H54" s="25" t="n"/>
+      <c r="I54" s="25" t="n"/>
     </row>
     <row r="55" ht="14" customHeight="1"/>
     <row r="56" ht="24" customHeight="1">
@@ -4557,7 +5065,7 @@
       </c>
     </row>
     <row r="61" ht="6" customHeight="1"/>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62" ht="22" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -4593,8 +5101,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="32" customHeight="1">
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="58" customHeight="1">
       <c r="A63" s="17" t="n">
         <v>1</v>
       </c>
@@ -4628,8 +5146,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>Whether the UE is configured to measure this E-UTRAN frequency in connected mode.</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="58" customHeight="1">
       <c r="A64" s="17" t="n">
         <v>2</v>
       </c>
@@ -4663,8 +5191,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>If selected, this frequency is forbidden as a handover target even if measured.</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="58" customHeight="1">
       <c r="A65" s="17" t="n">
         <v>3</v>
       </c>
@@ -4698,8 +5236,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>Per-neighbour flag allowing or prohibiting handover to that cell.</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="58" customHeight="1">
       <c r="A66" s="17" t="n">
         <v>4</v>
       </c>
@@ -4733,8 +5281,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>Maximum number of non-intra-frequency measurement objects the eNodeB may deliver to a UE.</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="58" customHeight="1">
       <c r="A67" s="17" t="n">
         <v>5</v>
       </c>
@@ -4768,8 +5326,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="32" customHeight="1">
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>Maximum number of neighbouring E-UTRAN FDD frequencies that can be delivered for measurement.</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="58" customHeight="1">
       <c r="A68" s="17" t="n">
         <v>6</v>
       </c>
@@ -4803,8 +5371,18 @@
           <t>4.1.5</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>Serving-cell RSRP above this value allows the UE to skip intra/inter/IRAT measurement.</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="58" customHeight="1">
       <c r="A69" s="17" t="n">
         <v>7</v>
       </c>
@@ -4838,8 +5416,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>Quantity (RSRP / RSRQ / BOTH) used to trigger inter-frequency events A1 and A2.</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
       <c r="A70" s="17" t="n">
         <v>8</v>
       </c>
@@ -4873,8 +5461,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="71" ht="32" customHeight="1">
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>Quantity used to trigger inter-frequency event A4.</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="58" customHeight="1">
       <c r="A71" s="17" t="n">
         <v>9</v>
       </c>
@@ -4908,8 +5506,18 @@
           <t>Table 4-8</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>Hysteresis Hys applied to entering and leaving conditions of events A1 and A2.</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="58" customHeight="1">
       <c r="A72" s="17" t="n">
         <v>10</v>
       </c>
@@ -4943,8 +5551,18 @@
           <t>Table 4-8</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>Duration TimeToTrig that A1/A2 entering or leaving condition must hold.</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="58" customHeight="1">
       <c r="A73" s="17" t="n">
         <v>11</v>
       </c>
@@ -4978,8 +5596,18 @@
           <t>Table 4-8</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="32" customHeight="1">
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>Hysteresis Hys in the event A4 formula.</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="58" customHeight="1">
       <c r="A74" s="17" t="n">
         <v>12</v>
       </c>
@@ -5013,8 +5641,18 @@
           <t>Table 4-9</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
+      <c r="H74" s="18" t="inlineStr">
+        <is>
+          <t>Duration TimeToTrig for event A4. 5120 ms is treated as disable for FreqPri / CQI / service IFHO.</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="58" customHeight="1">
       <c r="A75" s="17" t="n">
         <v>13</v>
       </c>
@@ -5048,8 +5686,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>Offset Off added on the serving side of intra-frequency event A3.</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="58" customHeight="1">
       <c r="A76" s="17" t="n">
         <v>14</v>
       </c>
@@ -5083,8 +5731,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>Offset Off added on the serving side of inter-frequency event A3.</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="58" customHeight="1">
       <c r="A77" s="17" t="n">
         <v>15</v>
       </c>
@@ -5118,8 +5776,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
+      <c r="H77" s="18" t="inlineStr">
+        <is>
+          <t>Cell-specific offset Ocn (CIO) for the neighbouring cell in A3/A4/A5.</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="58" customHeight="1">
       <c r="A78" s="17" t="n">
         <v>16</v>
       </c>
@@ -5153,8 +5821,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="32" customHeight="1">
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>Frequency-specific offset Ofn for the neighbouring frequency.</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="58" customHeight="1">
       <c r="A79" s="17" t="n">
         <v>17</v>
       </c>
@@ -5188,8 +5866,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>Layer-3 filter coefficient applied to RSRP before event evaluation.</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="58" customHeight="1">
       <c r="A80" s="17" t="n">
         <v>18</v>
       </c>
@@ -5223,8 +5911,18 @@
           <t>Table 4-4</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>Allows a higher-priority measurement algorithm to preempt gap resources of a limited-capability UE.</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="58" customHeight="1">
       <c r="A81" s="17" t="n">
         <v>19</v>
       </c>
@@ -5258,8 +5956,18 @@
           <t>4.1.4</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="44" customHeight="1">
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>Controls automatic delivery of measurement gap patterns for inter-frequency / IRAT measurement.</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="58" customHeight="1">
       <c r="A82" s="17" t="n">
         <v>20</v>
       </c>
@@ -5293,56 +6001,66 @@
           <t>Table 4-10</t>
         </is>
       </c>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>Priority used when several QCIs run together so the eNodeB knows which QCI’s HO parameters to deliver.</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="D53:I53"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="D51:I51"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="D54:I54"/>
+    <mergeCell ref="A9:I9"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="D52:I52"/>
     <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -5350,7 +6068,7 @@
     <hyperlink ref="C4" location="'05 Coverage HO'!A1" display="05 Coverage HO →"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  4 Basic Functions of Mobility Management in Connected Mode&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -5369,16 +6087,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5393,6 +6113,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -5511,6 +6233,8 @@
       <c r="E20" s="29" t="n"/>
       <c r="F20" s="29" t="n"/>
       <c r="G20" s="29" t="n"/>
+      <c r="H20" s="29" t="n"/>
+      <c r="I20" s="29" t="n"/>
     </row>
     <row r="21" ht="110" customHeight="1">
       <c r="A21" s="30" t="inlineStr">
@@ -5529,6 +6253,8 @@
       <c r="E21" s="29" t="n"/>
       <c r="F21" s="29" t="n"/>
       <c r="G21" s="29" t="n"/>
+      <c r="H21" s="29" t="n"/>
+      <c r="I21" s="29" t="n"/>
     </row>
     <row r="22" ht="10" customHeight="1"/>
     <row r="23" ht="22" customHeight="1">
@@ -5559,6 +6285,8 @@
       <c r="E27" s="14" t="n"/>
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -5572,6 +6300,8 @@
       <c r="E28" s="14" t="n"/>
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="6" customHeight="1"/>
     <row r="30" ht="18" customHeight="1">
@@ -5586,6 +6316,8 @@
       <c r="E30" s="29" t="n"/>
       <c r="F30" s="29" t="n"/>
       <c r="G30" s="29" t="n"/>
+      <c r="H30" s="29" t="n"/>
+      <c r="I30" s="29" t="n"/>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
@@ -5599,6 +6331,8 @@
       <c r="E31" s="29" t="n"/>
       <c r="F31" s="29" t="n"/>
       <c r="G31" s="29" t="n"/>
+      <c r="H31" s="29" t="n"/>
+      <c r="I31" s="29" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="22" t="inlineStr">
@@ -5616,6 +6350,8 @@
       <c r="E32" s="25" t="n"/>
       <c r="F32" s="25" t="n"/>
       <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
@@ -5633,6 +6369,8 @@
       <c r="E33" s="25" t="n"/>
       <c r="F33" s="25" t="n"/>
       <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -5650,6 +6388,8 @@
       <c r="E34" s="25" t="n"/>
       <c r="F34" s="25" t="n"/>
       <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
     </row>
     <row r="35" ht="6" customHeight="1"/>
     <row r="36" ht="18" customHeight="1">
@@ -5664,6 +6404,8 @@
       <c r="E36" s="32" t="n"/>
       <c r="F36" s="32" t="n"/>
       <c r="G36" s="32" t="n"/>
+      <c r="H36" s="32" t="n"/>
+      <c r="I36" s="32" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
@@ -5677,6 +6419,8 @@
       <c r="E37" s="32" t="n"/>
       <c r="F37" s="32" t="n"/>
       <c r="G37" s="32" t="n"/>
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="32" t="n"/>
     </row>
     <row r="38" ht="10" customHeight="1"/>
     <row r="39" ht="22" customHeight="1">
@@ -5707,6 +6451,8 @@
       <c r="E43" s="14" t="n"/>
       <c r="F43" s="14" t="n"/>
       <c r="G43" s="14" t="n"/>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="14" t="n"/>
     </row>
     <row r="44" ht="98" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
@@ -5723,6 +6469,8 @@
       <c r="E44" s="14" t="n"/>
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="6" customHeight="1"/>
     <row r="46" ht="18" customHeight="1">
@@ -5737,6 +6485,8 @@
       <c r="E46" s="29" t="n"/>
       <c r="F46" s="29" t="n"/>
       <c r="G46" s="29" t="n"/>
+      <c r="H46" s="29" t="n"/>
+      <c r="I46" s="29" t="n"/>
     </row>
     <row r="47" ht="84" customHeight="1">
       <c r="A47" s="30" t="inlineStr">
@@ -5752,6 +6502,8 @@
       <c r="E47" s="29" t="n"/>
       <c r="F47" s="29" t="n"/>
       <c r="G47" s="29" t="n"/>
+      <c r="H47" s="29" t="n"/>
+      <c r="I47" s="29" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
@@ -5769,6 +6521,8 @@
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="25" t="n"/>
       <c r="G48" s="25" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
@@ -5786,6 +6540,8 @@
       <c r="E49" s="25" t="n"/>
       <c r="F49" s="25" t="n"/>
       <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
@@ -5803,6 +6559,8 @@
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="25" t="n"/>
       <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="26" t="inlineStr"/>
@@ -5816,6 +6574,8 @@
       <c r="E51" s="25" t="n"/>
       <c r="F51" s="25" t="n"/>
       <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
     </row>
     <row r="52" ht="6" customHeight="1"/>
     <row r="53" ht="18" customHeight="1">
@@ -5830,6 +6590,8 @@
       <c r="E53" s="32" t="n"/>
       <c r="F53" s="32" t="n"/>
       <c r="G53" s="32" t="n"/>
+      <c r="H53" s="32" t="n"/>
+      <c r="I53" s="32" t="n"/>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="33" t="inlineStr">
@@ -5843,6 +6605,8 @@
       <c r="E54" s="32" t="n"/>
       <c r="F54" s="32" t="n"/>
       <c r="G54" s="32" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="32" t="n"/>
     </row>
     <row r="55" ht="10" customHeight="1"/>
     <row r="56" ht="22" customHeight="1">
@@ -5873,6 +6637,8 @@
       <c r="E60" s="14" t="n"/>
       <c r="F60" s="14" t="n"/>
       <c r="G60" s="14" t="n"/>
+      <c r="H60" s="14" t="n"/>
+      <c r="I60" s="14" t="n"/>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
@@ -5886,6 +6652,8 @@
       <c r="E61" s="14" t="n"/>
       <c r="F61" s="14" t="n"/>
       <c r="G61" s="14" t="n"/>
+      <c r="H61" s="14" t="n"/>
+      <c r="I61" s="14" t="n"/>
     </row>
     <row r="62" ht="6" customHeight="1"/>
     <row r="63" ht="18" customHeight="1">
@@ -5900,6 +6668,8 @@
       <c r="E63" s="29" t="n"/>
       <c r="F63" s="29" t="n"/>
       <c r="G63" s="29" t="n"/>
+      <c r="H63" s="29" t="n"/>
+      <c r="I63" s="29" t="n"/>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="30" t="inlineStr">
@@ -5913,6 +6683,8 @@
       <c r="E64" s="29" t="n"/>
       <c r="F64" s="29" t="n"/>
       <c r="G64" s="29" t="n"/>
+      <c r="H64" s="29" t="n"/>
+      <c r="I64" s="29" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="22" t="inlineStr">
@@ -5930,6 +6702,8 @@
       <c r="E65" s="25" t="n"/>
       <c r="F65" s="25" t="n"/>
       <c r="G65" s="25" t="n"/>
+      <c r="H65" s="25" t="n"/>
+      <c r="I65" s="25" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="26" t="inlineStr">
@@ -5947,6 +6721,8 @@
       <c r="E66" s="25" t="n"/>
       <c r="F66" s="25" t="n"/>
       <c r="G66" s="25" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="25" t="n"/>
     </row>
     <row r="67" ht="10" customHeight="1"/>
     <row r="68" ht="22" customHeight="1">
@@ -5977,6 +6753,8 @@
       <c r="E72" s="14" t="n"/>
       <c r="F72" s="14" t="n"/>
       <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
@@ -5990,6 +6768,8 @@
       <c r="E73" s="14" t="n"/>
       <c r="F73" s="14" t="n"/>
       <c r="G73" s="14" t="n"/>
+      <c r="H73" s="14" t="n"/>
+      <c r="I73" s="14" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="22" t="inlineStr">
@@ -6007,6 +6787,8 @@
       <c r="E74" s="25" t="n"/>
       <c r="F74" s="25" t="n"/>
       <c r="G74" s="25" t="n"/>
+      <c r="H74" s="25" t="n"/>
+      <c r="I74" s="25" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="26" t="inlineStr">
@@ -6024,6 +6806,8 @@
       <c r="E75" s="25" t="n"/>
       <c r="F75" s="25" t="n"/>
       <c r="G75" s="25" t="n"/>
+      <c r="H75" s="25" t="n"/>
+      <c r="I75" s="25" t="n"/>
     </row>
     <row r="76" ht="10" customHeight="1"/>
     <row r="77" ht="22" customHeight="1">
@@ -6054,6 +6838,8 @@
       <c r="E81" s="14" t="n"/>
       <c r="F81" s="14" t="n"/>
       <c r="G81" s="14" t="n"/>
+      <c r="H81" s="14" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
@@ -6067,6 +6853,8 @@
       <c r="E82" s="14" t="n"/>
       <c r="F82" s="14" t="n"/>
       <c r="G82" s="14" t="n"/>
+      <c r="H82" s="14" t="n"/>
+      <c r="I82" s="14" t="n"/>
     </row>
     <row r="83" ht="6" customHeight="1"/>
     <row r="84" ht="18" customHeight="1">
@@ -6081,6 +6869,8 @@
       <c r="E84" s="32" t="n"/>
       <c r="F84" s="32" t="n"/>
       <c r="G84" s="32" t="n"/>
+      <c r="H84" s="32" t="n"/>
+      <c r="I84" s="32" t="n"/>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="33" t="inlineStr">
@@ -6094,6 +6884,8 @@
       <c r="E85" s="32" t="n"/>
       <c r="F85" s="32" t="n"/>
       <c r="G85" s="32" t="n"/>
+      <c r="H85" s="32" t="n"/>
+      <c r="I85" s="32" t="n"/>
     </row>
     <row r="86" ht="14" customHeight="1"/>
     <row r="87" ht="24" customHeight="1">
@@ -6120,7 +6912,7 @@
       </c>
     </row>
     <row r="92" ht="6" customHeight="1"/>
-    <row r="93" ht="20" customHeight="1">
+    <row r="93" ht="22" customHeight="1">
       <c r="A93" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -6156,8 +6948,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
+      <c r="H93" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="58" customHeight="1">
       <c r="A94" s="17" t="n">
         <v>1</v>
       </c>
@@ -6191,8 +6993,18 @@
           <t>5.2 Intra-freq</t>
         </is>
       </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>Enables coverage-based intra-frequency handover (event A3).</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201801  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="58" customHeight="1">
       <c r="A95" s="17" t="n">
         <v>2</v>
       </c>
@@ -6226,8 +7038,18 @@
           <t>5.2 Intra-freq</t>
         </is>
       </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>Measurement quantity that triggers intra-frequency event A3.</t>
+        </is>
+      </c>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201801  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="58" customHeight="1">
       <c r="A96" s="17" t="n">
         <v>3</v>
       </c>
@@ -6261,8 +7083,18 @@
           <t>5.2 Intra-freq</t>
         </is>
       </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>Offset Off in the intra-frequency A3 formula (Mn+Ofn+Ocn−Hys &gt; Ms+Ofs+Ocs+Off).</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201801  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.2 / §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="58" customHeight="1">
       <c r="A97" s="17" t="n">
         <v>4</v>
       </c>
@@ -6296,8 +7128,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="98" ht="32" customHeight="1">
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>Enables coverage-based inter-frequency handover (measurement-based and related blind options).</t>
+        </is>
+      </c>
+      <c r="I97" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="58" customHeight="1">
       <c r="A98" s="17" t="n">
         <v>5</v>
       </c>
@@ -6331,8 +7173,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
+      <c r="H98" s="18" t="inlineStr">
+        <is>
+          <t>When ON, an inter-frequency A2 starts preferential blind HO instead of measurement-based IFHO.</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="58" customHeight="1">
       <c r="A99" s="17" t="n">
         <v>6</v>
       </c>
@@ -6366,8 +7218,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="100" ht="32" customHeight="1">
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>Enables emergency blind redirection when serving quality is too poor to complete measurement.</t>
+        </is>
+      </c>
+      <c r="I99" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="58" customHeight="1">
       <c r="A100" s="17" t="n">
         <v>7</v>
       </c>
@@ -6401,8 +7263,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="101" ht="32" customHeight="1">
+      <c r="H100" s="18" t="inlineStr">
+        <is>
+          <t>Chooses the target event (A3 / A4 / A5) and therefore which coverage A2 family is delivered.</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.1.4 / §5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="58" customHeight="1">
       <c r="A101" s="17" t="n">
         <v>8</v>
       </c>
@@ -6436,8 +7308,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="102" ht="32" customHeight="1">
+      <c r="H101" s="18" t="inlineStr">
+        <is>
+          <t>Event A2 RSRP threshold used when the inter-frequency target event is A3. Effective thd = this + operator/QCI offset.</t>
+        </is>
+      </c>
+      <c r="I101" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 5-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="58" customHeight="1">
       <c r="A102" s="17" t="n">
         <v>9</v>
       </c>
@@ -6471,8 +7353,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="103" ht="32" customHeight="1">
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>Event A2 RSRP threshold used when the inter-frequency target event is A4 or A5.</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 5-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="58" customHeight="1">
       <c r="A103" s="17" t="n">
         <v>10</v>
       </c>
@@ -6506,8 +7398,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
+      <c r="H103" s="18" t="inlineStr">
+        <is>
+          <t>Absolute neighbour RSRP threshold for coverage inter-frequency event A4.</t>
+        </is>
+      </c>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="58" customHeight="1">
       <c r="A104" s="17" t="n">
         <v>11</v>
       </c>
@@ -6541,8 +7443,18 @@
           <t>5.3 Blind</t>
         </is>
       </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
+      <c r="H104" s="18" t="inlineStr">
+        <is>
+          <t>Event A2 RSRP threshold that starts coverage blind inter-frequency / IRAT handling.</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="58" customHeight="1">
       <c r="A105" s="17" t="n">
         <v>12</v>
       </c>
@@ -6576,8 +7488,18 @@
           <t>5.3 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
+      <c r="H105" s="18" t="inlineStr">
+        <is>
+          <t>Delivers A2 measurement first at RRC setup and A1 only after A2, to reduce extra A1/A2 signalling.</t>
+        </is>
+      </c>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201802  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="58" customHeight="1">
       <c r="A106" s="17" t="n">
         <v>13</v>
       </c>
@@ -6611,8 +7533,18 @@
           <t>5.4 UTRAN</t>
         </is>
       </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
+      <c r="H106" s="18" t="inlineStr">
+        <is>
+          <t>Enables measurement-based PS handover from E-UTRAN to UTRAN.</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001019  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="58" customHeight="1">
       <c r="A107" s="17" t="n">
         <v>14</v>
       </c>
@@ -6646,8 +7578,18 @@
           <t>5.4 UTRAN</t>
         </is>
       </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>Enables redirection (blind path) from E-UTRAN to UTRAN.</t>
+        </is>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001019  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="58" customHeight="1">
       <c r="A108" s="17" t="n">
         <v>15</v>
       </c>
@@ -6681,8 +7623,18 @@
           <t>5.4 / 5.5</t>
         </is>
       </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
+      <c r="H108" s="18" t="inlineStr">
+        <is>
+          <t>Quantity used to trigger inter-RAT events A1 and A2.</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001019  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="58" customHeight="1">
       <c r="A109" s="17" t="n">
         <v>16</v>
       </c>
@@ -6716,8 +7668,18 @@
           <t>5.4 / 5.5</t>
         </is>
       </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>Serving-cell A2 RSRP threshold that starts coverage inter-RAT measurement.</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001019  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="58" customHeight="1">
       <c r="A110" s="17" t="n">
         <v>17</v>
       </c>
@@ -6751,8 +7713,18 @@
           <t>5.5 GERAN</t>
         </is>
       </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
+      <c r="H110" s="18" t="inlineStr">
+        <is>
+          <t>Enables coverage-based handover / redirection from E-UTRAN to GERAN.</t>
+        </is>
+      </c>
+      <c r="I110" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001020  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="58" customHeight="1">
       <c r="A111" s="17" t="n">
         <v>18</v>
       </c>
@@ -6786,8 +7758,18 @@
           <t>5.6 CS/PS</t>
         </is>
       </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>Enables measurement-based CS/PS frequency-layer steering toward UTRAN.</t>
+        </is>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001078  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="58" customHeight="1">
       <c r="A112" s="17" t="n">
         <v>19</v>
       </c>
@@ -6821,8 +7803,18 @@
           <t>5.6 CS/PS</t>
         </is>
       </c>
-    </row>
-    <row r="113" ht="32" customHeight="1">
+      <c r="H112" s="18" t="inlineStr">
+        <is>
+          <t>Enables blind CS/PS frequency-layer steering toward UTRAN.</t>
+        </is>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001078  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="58" customHeight="1">
       <c r="A113" s="17" t="n">
         <v>20</v>
       </c>
@@ -6856,8 +7848,18 @@
           <t>5.6 CS/PS</t>
         </is>
       </c>
-    </row>
-    <row r="114" ht="32" customHeight="1">
+      <c r="H113" s="18" t="inlineStr">
+        <is>
+          <t>Priority of a neighbouring UTRAN frequency for CS services versus PS services. Priority_0 = not used for that service.</t>
+        </is>
+      </c>
+      <c r="I113" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001078  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §5.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="58" customHeight="1">
       <c r="A114" s="17" t="n">
         <v>21</v>
       </c>
@@ -6891,8 +7893,18 @@
           <t>5.1.5</t>
         </is>
       </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
+      <c r="H114" s="18" t="inlineStr">
+        <is>
+          <t>After IRAT A2, restricts measurement to the highest-priority RAT for QCI-1 / SRVCC.</t>
+        </is>
+      </c>
+      <c r="I114" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001019  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 5-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="58" customHeight="1">
       <c r="A115" s="17" t="n">
         <v>22</v>
       </c>
@@ -6926,80 +7938,90 @@
           <t>5.1.5</t>
         </is>
       </c>
+      <c r="H115" s="18" t="inlineStr">
+        <is>
+          <t>After IRAT A2, restricts measurement to the highest-priority RAT for data (non-QCI-1) services.</t>
+        </is>
+      </c>
+      <c r="I115" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001019  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 5-4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="D49:I49"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A46:I46"/>
     <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A91:G91"/>
-    <mergeCell ref="D74:G74"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A89:I89"/>
     <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="D48:I48"/>
+    <mergeCell ref="D66:I66"/>
     <mergeCell ref="A50:C50"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="D75:I75"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A85:I85"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A91:I91"/>
+    <mergeCell ref="D74:I74"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="D51:I51"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="D50:I50"/>
+    <mergeCell ref="A58:I58"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A77:I77"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A30:I30"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A73:I73"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="D66:G66"/>
-    <mergeCell ref="D75:G75"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D65:I65"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A87:I87"/>
     <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -7008,7 +8030,7 @@
     <hyperlink ref="D4" location="'04 Basic Functions'!A1" display="Ch.4 Basic (must)"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  5 Coverage-based Handover&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -7027,16 +8049,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -7051,6 +8075,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7155,6 +8181,8 @@
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="32" t="n"/>
       <c r="G18" s="32" t="n"/>
+      <c r="H18" s="32" t="n"/>
+      <c r="I18" s="32" t="n"/>
     </row>
     <row r="19" ht="110" customHeight="1">
       <c r="A19" s="33" t="inlineStr">
@@ -7171,6 +8199,8 @@
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="32" t="n"/>
       <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="32" t="n"/>
     </row>
     <row r="20" ht="10" customHeight="1"/>
     <row r="21" ht="22" customHeight="1">
@@ -7194,6 +8224,8 @@
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -7207,6 +8239,8 @@
       <c r="E25" s="14" t="n"/>
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="6" customHeight="1"/>
     <row r="27" ht="18" customHeight="1">
@@ -7221,6 +8255,8 @@
       <c r="E27" s="29" t="n"/>
       <c r="F27" s="29" t="n"/>
       <c r="G27" s="29" t="n"/>
+      <c r="H27" s="29" t="n"/>
+      <c r="I27" s="29" t="n"/>
     </row>
     <row r="28" ht="110" customHeight="1">
       <c r="A28" s="30" t="inlineStr">
@@ -7238,6 +8274,8 @@
       <c r="E28" s="29" t="n"/>
       <c r="F28" s="29" t="n"/>
       <c r="G28" s="29" t="n"/>
+      <c r="H28" s="29" t="n"/>
+      <c r="I28" s="29" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="22" t="inlineStr">
@@ -7255,6 +8293,8 @@
       <c r="E29" s="25" t="n"/>
       <c r="F29" s="25" t="n"/>
       <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -7272,6 +8312,8 @@
       <c r="E30" s="25" t="n"/>
       <c r="F30" s="25" t="n"/>
       <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
@@ -7289,6 +8331,8 @@
       <c r="E31" s="25" t="n"/>
       <c r="F31" s="25" t="n"/>
       <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="26" t="inlineStr"/>
@@ -7302,6 +8346,8 @@
       <c r="E32" s="25" t="n"/>
       <c r="F32" s="25" t="n"/>
       <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
     </row>
     <row r="33" ht="10" customHeight="1"/>
     <row r="34" ht="22" customHeight="1">
@@ -7325,6 +8371,8 @@
       <c r="E37" s="14" t="n"/>
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -7338,6 +8386,8 @@
       <c r="E38" s="14" t="n"/>
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="40" ht="18" customHeight="1">
@@ -7352,6 +8402,8 @@
       <c r="E40" s="29" t="n"/>
       <c r="F40" s="29" t="n"/>
       <c r="G40" s="29" t="n"/>
+      <c r="H40" s="29" t="n"/>
+      <c r="I40" s="29" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="30" t="inlineStr">
@@ -7365,6 +8417,8 @@
       <c r="E41" s="29" t="n"/>
       <c r="F41" s="29" t="n"/>
       <c r="G41" s="29" t="n"/>
+      <c r="H41" s="29" t="n"/>
+      <c r="I41" s="29" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
@@ -7382,6 +8436,8 @@
       <c r="E42" s="25" t="n"/>
       <c r="F42" s="25" t="n"/>
       <c r="G42" s="25" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
@@ -7399,6 +8455,8 @@
       <c r="E43" s="25" t="n"/>
       <c r="F43" s="25" t="n"/>
       <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
     </row>
     <row r="44" ht="10" customHeight="1"/>
     <row r="45" ht="22" customHeight="1">
@@ -7422,6 +8480,8 @@
       <c r="E48" s="14" t="n"/>
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
@@ -7435,6 +8495,8 @@
       <c r="E49" s="14" t="n"/>
       <c r="F49" s="14" t="n"/>
       <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
@@ -7452,6 +8514,8 @@
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="25" t="n"/>
       <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
@@ -7469,6 +8533,8 @@
       <c r="E51" s="25" t="n"/>
       <c r="F51" s="25" t="n"/>
       <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
     </row>
     <row r="52" ht="14" customHeight="1"/>
     <row r="53" ht="24" customHeight="1">
@@ -7495,7 +8561,7 @@
       </c>
     </row>
     <row r="58" ht="6" customHeight="1"/>
-    <row r="59" ht="20" customHeight="1">
+    <row r="59" ht="22" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -7531,8 +8597,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="58" customHeight="1">
       <c r="A60" s="17" t="n">
         <v>1</v>
       </c>
@@ -7566,8 +8642,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="32" customHeight="1">
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>eNodeB-level switch that enables service-based inter-frequency handover.</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="58" customHeight="1">
       <c r="A61" s="17" t="n">
         <v>2</v>
       </c>
@@ -7601,8 +8687,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="32" customHeight="1">
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>Cell-level switch that allows service-based inter-frequency handover in this cell. Both eNodeB and cell bits are required.</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="58" customHeight="1">
       <c r="A62" s="17" t="n">
         <v>3</v>
       </c>
@@ -7636,8 +8732,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>Whether a QCI bound to this group is permitted to leave the serving frequency by service-based HO.</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="58" customHeight="1">
       <c r="A63" s="17" t="n">
         <v>4</v>
       </c>
@@ -7671,8 +8777,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>Links a QCI of an operator to a ServiceIfHoCfgGroup (target-frequency policy).</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="58" customHeight="1">
       <c r="A64" s="17" t="n">
         <v>5</v>
       </c>
@@ -7706,8 +8822,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="32" customHeight="1">
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>Downlink EARFCN that may carry the QCI after service-based inter-frequency HO.</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.2 / LOFD-171207</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="58" customHeight="1">
       <c r="A65" s="17" t="n">
         <v>6</v>
       </c>
@@ -7741,8 +8867,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>Base A4 RSRP threshold for service-based IFHO. Effective thd = this + QCI/operator offset.</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 6-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="58" customHeight="1">
       <c r="A66" s="17" t="n">
         <v>7</v>
       </c>
@@ -7776,8 +8912,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="32" customHeight="1">
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>TimeToTrig for the A4 used by service-based IFHO. 5120 ms disables the function.</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-9 / §6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="58" customHeight="1">
       <c r="A67" s="17" t="n">
         <v>8</v>
       </c>
@@ -7811,8 +8957,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="32" customHeight="1">
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>When ON, CA-incapable UEs prefer high-priority, high-bandwidth, light-load targets; CA-capable UEs are not service-HO’d.</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-171207  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="58" customHeight="1">
       <c r="A68" s="17" t="n">
         <v>9</v>
       </c>
@@ -7846,8 +9002,18 @@
           <t>6.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>Allows a later service-based HO to select the previous source frequency as target.</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201805  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="58" customHeight="1">
       <c r="A69" s="17" t="n">
         <v>10</v>
       </c>
@@ -7881,8 +9047,18 @@
           <t>6.3 UTRAN</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>Enables service-based inter-RAT handover to UTRAN for bound QCIs.</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001043  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
       <c r="A70" s="17" t="n">
         <v>11</v>
       </c>
@@ -7916,8 +9092,18 @@
           <t>6.4 GERAN</t>
         </is>
       </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>Enables service-based inter-RAT handover to GERAN for bound QCIs.</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001046  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="58" customHeight="1">
       <c r="A71" s="17" t="n">
         <v>12</v>
       </c>
@@ -7951,53 +9137,63 @@
           <t>6.3 / 6.4</t>
         </is>
       </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>Inter-RAT policy for the QCI: MUST_HO forces IRAT; PERMIT_HO allows it.</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001043  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §6.3 / §6.4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A50:C50"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="D51:I51"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="D29:I29"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A9:I9"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="D50:I50"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -8006,7 +9202,7 @@
     <hyperlink ref="D4" location="'04 Basic Functions'!A1" display="Ch.4 Basic (must)"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  6 Service-based Handover&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -8025,16 +9221,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8049,6 +9247,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -8153,6 +9353,8 @@
       <c r="E18" s="29" t="n"/>
       <c r="F18" s="29" t="n"/>
       <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
     </row>
     <row r="19" ht="98" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
@@ -8169,6 +9371,8 @@
       <c r="E19" s="29" t="n"/>
       <c r="F19" s="29" t="n"/>
       <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
     </row>
     <row r="20" ht="10" customHeight="1"/>
     <row r="21" ht="22" customHeight="1">
@@ -8192,6 +9396,8 @@
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -8205,6 +9411,8 @@
       <c r="E25" s="14" t="n"/>
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
@@ -8222,6 +9430,8 @@
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="25" t="n"/>
       <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -8239,6 +9449,8 @@
       <c r="E27" s="25" t="n"/>
       <c r="F27" s="25" t="n"/>
       <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
@@ -8256,6 +9468,8 @@
       <c r="E28" s="25" t="n"/>
       <c r="F28" s="25" t="n"/>
       <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="26" t="inlineStr"/>
@@ -8269,6 +9483,8 @@
       <c r="E29" s="25" t="n"/>
       <c r="F29" s="25" t="n"/>
       <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
     </row>
     <row r="30" ht="10" customHeight="1"/>
     <row r="31" ht="22" customHeight="1">
@@ -8292,6 +9508,8 @@
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
@@ -8305,6 +9523,8 @@
       <c r="E35" s="14" t="n"/>
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36" ht="6" customHeight="1"/>
     <row r="37" ht="18" customHeight="1">
@@ -8319,6 +9539,8 @@
       <c r="E37" s="32" t="n"/>
       <c r="F37" s="32" t="n"/>
       <c r="G37" s="32" t="n"/>
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="32" t="n"/>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="33" t="inlineStr">
@@ -8332,6 +9554,8 @@
       <c r="E38" s="32" t="n"/>
       <c r="F38" s="32" t="n"/>
       <c r="G38" s="32" t="n"/>
+      <c r="H38" s="32" t="n"/>
+      <c r="I38" s="32" t="n"/>
     </row>
     <row r="39" ht="14" customHeight="1"/>
     <row r="40" ht="24" customHeight="1">
@@ -8358,7 +9582,7 @@
       </c>
     </row>
     <row r="45" ht="6" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46" ht="22" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -8394,8 +9618,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
       <c r="A47" s="17" t="n">
         <v>1</v>
       </c>
@@ -8429,8 +9663,18 @@
           <t>7.x All</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>Master switch that enables distance-based handover (TA-based overshoot control).</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201804  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
       <c r="A48" s="17" t="n">
         <v>2</v>
       </c>
@@ -8464,8 +9708,18 @@
           <t>7.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>Selects E-UTRAN as the measurement / target RAT for distance-based HO.</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201804  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
       <c r="A49" s="17" t="n">
         <v>3</v>
       </c>
@@ -8499,8 +9753,18 @@
           <t>7.3 UTRAN</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>Selects UTRAN as a distance-based HO target RAT.</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001072  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §7.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
       <c r="A50" s="17" t="n">
         <v>4</v>
       </c>
@@ -8534,8 +9798,18 @@
           <t>7.4 GERAN</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="32" customHeight="1">
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>Selects GERAN as a distance-based HO target RAT.</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>LOFD-001073  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §7.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
       <c r="A51" s="17" t="n">
         <v>5</v>
       </c>
@@ -8569,8 +9843,18 @@
           <t>7.2</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>Distance threshold. HO measurement starts when TA-estimated distance exceeds this for 10 seconds.</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201804  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 7-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
       <c r="A52" s="17" t="n">
         <v>6</v>
       </c>
@@ -8604,8 +9888,18 @@
           <t>7.2</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>A4 RSRP threshold used to qualify the LTE target after distance trigger.</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201804  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 7-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
       <c r="A53" s="17" t="n">
         <v>7</v>
       </c>
@@ -8639,40 +9933,50 @@
           <t>7.2</t>
         </is>
       </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>Quantity used to trigger the A4 that qualifies a distance-based LTE target.</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-00201804  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 7-5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A18:I18"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A14:I14"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -8681,7 +9985,7 @@
     <hyperlink ref="D4" location="'04 Basic Functions'!A1" display="Ch.4 Basic (must)"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  7 Distance-based Handover&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -8700,16 +10004,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8724,6 +10030,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -8830,6 +10138,8 @@
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -8843,6 +10153,8 @@
       <c r="E21" s="14" t="n"/>
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="6" customHeight="1"/>
     <row r="23" ht="18" customHeight="1">
@@ -8857,6 +10169,8 @@
       <c r="E23" s="29" t="n"/>
       <c r="F23" s="29" t="n"/>
       <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
     </row>
     <row r="24" ht="110" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
@@ -8874,6 +10188,8 @@
       <c r="E24" s="29" t="n"/>
       <c r="F24" s="29" t="n"/>
       <c r="G24" s="29" t="n"/>
+      <c r="H24" s="29" t="n"/>
+      <c r="I24" s="29" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
@@ -8891,6 +10207,8 @@
       <c r="E25" s="25" t="n"/>
       <c r="F25" s="25" t="n"/>
       <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
@@ -8908,6 +10226,8 @@
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="25" t="n"/>
       <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
@@ -8925,6 +10245,8 @@
       <c r="E27" s="25" t="n"/>
       <c r="F27" s="25" t="n"/>
       <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="26" t="inlineStr"/>
@@ -8938,6 +10260,8 @@
       <c r="E28" s="25" t="n"/>
       <c r="F28" s="25" t="n"/>
       <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
     </row>
     <row r="29" ht="10" customHeight="1"/>
     <row r="30" ht="22" customHeight="1">
@@ -8961,6 +10285,8 @@
       <c r="E33" s="14" t="n"/>
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="n"/>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -8974,6 +10300,8 @@
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="6" customHeight="1"/>
     <row r="36" ht="18" customHeight="1">
@@ -8988,6 +10316,8 @@
       <c r="E36" s="32" t="n"/>
       <c r="F36" s="32" t="n"/>
       <c r="G36" s="32" t="n"/>
+      <c r="H36" s="32" t="n"/>
+      <c r="I36" s="32" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
@@ -9001,6 +10331,8 @@
       <c r="E37" s="32" t="n"/>
       <c r="F37" s="32" t="n"/>
       <c r="G37" s="32" t="n"/>
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="32" t="n"/>
     </row>
     <row r="38" ht="14" customHeight="1"/>
     <row r="39" ht="24" customHeight="1">
@@ -9027,7 +10359,7 @@
       </c>
     </row>
     <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="22" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -9063,8 +10395,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
       <c r="A46" s="17" t="n">
         <v>1</v>
       </c>
@@ -9098,8 +10440,18 @@
           <t>8.2 Inter-freq</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>Enables UL-quality-based inter-frequency handover (measurement-based and blind).</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §8.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
       <c r="A47" s="17" t="n">
         <v>2</v>
       </c>
@@ -9133,8 +10485,18 @@
           <t>8.3 IRAT</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>Enables UL-quality-based inter-RAT handover to UTRAN or GERAN.</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §8.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
       <c r="A48" s="17" t="n">
         <v>3</v>
       </c>
@@ -9168,8 +10530,18 @@
           <t>8.2</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>Uplink MCS index threshold. Measurement starts when UL MCS is below this value (together with IBLER gap).</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 8-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
       <c r="A49" s="17" t="n">
         <v>4</v>
       </c>
@@ -9203,8 +10575,18 @@
           <t>8.2</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>IBLER-gap threshold. Measurement starts when (actual IBLER − target IBLER) exceeds this value.</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 8-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
       <c r="A50" s="17" t="n">
         <v>5</v>
       </c>
@@ -9238,8 +10620,18 @@
           <t>8.2</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="32" customHeight="1">
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>Base A4 RSRP threshold for UL-quality IFHO before the UL-quality offset is added.</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
       <c r="A51" s="17" t="n">
         <v>6</v>
       </c>
@@ -9273,8 +10665,18 @@
           <t>8.2</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>Offset added to the A4 RSRP/RSRQ threshold for UL-quality-based HO only. Effective A4 = base + this offset.</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
       <c r="A52" s="17" t="n">
         <v>7</v>
       </c>
@@ -9308,39 +10710,49 @@
           <t>8.2</t>
         </is>
       </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>Quantity used to trigger the A4 that qualifies a UL-quality LTE target.</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 8-5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A37:I37"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="D25:I25"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -9349,7 +10761,7 @@
     <hyperlink ref="D4" location="'04 Basic Functions'!A1" display="Ch.4 Basic (must)"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  8 UL-Quality-based Handover&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -9368,16 +10780,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9392,6 +10806,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -9475,6 +10891,8 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="110" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -9491,6 +10909,8 @@
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
@@ -9505,6 +10925,8 @@
       <c r="E18" s="29" t="n"/>
       <c r="F18" s="29" t="n"/>
       <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
     </row>
     <row r="19" ht="84" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
@@ -9520,6 +10942,8 @@
       <c r="E19" s="29" t="n"/>
       <c r="F19" s="29" t="n"/>
       <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
@@ -9537,6 +10961,8 @@
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="25" t="n"/>
       <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -9554,6 +10980,8 @@
       <c r="E21" s="25" t="n"/>
       <c r="F21" s="25" t="n"/>
       <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -9571,6 +10999,8 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="25" t="n"/>
       <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="26" t="inlineStr"/>
@@ -9584,6 +11014,8 @@
       <c r="E23" s="25" t="n"/>
       <c r="F23" s="25" t="n"/>
       <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="26" t="inlineStr"/>
@@ -9597,6 +11029,8 @@
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="25" t="n"/>
       <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="6" customHeight="1"/>
     <row r="26" ht="18" customHeight="1">
@@ -9611,6 +11045,8 @@
       <c r="E26" s="32" t="n"/>
       <c r="F26" s="32" t="n"/>
       <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="33" t="inlineStr">
@@ -9624,6 +11060,8 @@
       <c r="E27" s="32" t="n"/>
       <c r="F27" s="32" t="n"/>
       <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
     </row>
     <row r="28" ht="14" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
@@ -9650,7 +11088,7 @@
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -9686,8 +11124,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
       <c r="A36" s="17" t="n">
         <v>1</v>
       </c>
@@ -9721,8 +11169,18 @@
           <t>9 CQI</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>Enables CQI-based inter-frequency handover (FDD). Starts when serving CQI is poor while coverage A2 may not have fired.</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
       <c r="A37" s="17" t="n">
         <v>2</v>
       </c>
@@ -9756,8 +11214,18 @@
           <t>9 CQI</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>TimeToTrig for A4. 5120 ms disables CQI-based IFHO.</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-9 / §9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
       <c r="A38" s="17" t="n">
         <v>3</v>
       </c>
@@ -9791,8 +11259,18 @@
           <t>9 CQI</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>Absolute neighbour RSRP threshold of event A4 used to qualify the CQI-based IFHO target.</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
       <c r="A39" s="17" t="n">
         <v>4</v>
       </c>
@@ -9826,8 +11304,18 @@
           <t>9 CQI</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>Hysteresis Hys in the A4 formula for CQI-based IFHO.</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8 / §9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
       <c r="A40" s="17" t="n">
         <v>5</v>
       </c>
@@ -9861,8 +11349,18 @@
           <t>9 CQI</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Quantity used to trigger event A4 for CQI-based IFHO.</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
       <c r="A41" s="17" t="n">
         <v>6</v>
       </c>
@@ -9896,35 +11394,45 @@
           <t>→ Ch.4</t>
         </is>
       </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>Whether this frequency is included in connected-mode measurement. Required for any IFHO including CQI-based.</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="D20:G20"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="D20:I20"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -9934,7 +11442,7 @@
     <hyperlink ref="G41" location="'04 Basic Functions'!A1" display="→ Ch.4"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  9 CQI-based Inter-Frequency Handover (FDD)&amp;RPage &amp;P of &amp;N</oddFooter>
@@ -9953,16 +11461,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
-    <col width="3.2" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9977,6 +11487,8 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -10060,6 +11572,8 @@
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="98" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -10076,6 +11590,8 @@
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
@@ -10090,6 +11606,8 @@
       <c r="E18" s="29" t="n"/>
       <c r="F18" s="29" t="n"/>
       <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
     </row>
     <row r="19" ht="110" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
@@ -10106,6 +11624,8 @@
       <c r="E19" s="29" t="n"/>
       <c r="F19" s="29" t="n"/>
       <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
@@ -10123,6 +11643,8 @@
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="25" t="n"/>
       <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -10140,6 +11662,8 @@
       <c r="E21" s="25" t="n"/>
       <c r="F21" s="25" t="n"/>
       <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -10157,6 +11681,8 @@
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="25" t="n"/>
       <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="26" t="inlineStr"/>
@@ -10170,6 +11696,8 @@
       <c r="E23" s="25" t="n"/>
       <c r="F23" s="25" t="n"/>
       <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="6" customHeight="1"/>
     <row r="25" ht="18" customHeight="1">
@@ -10184,6 +11712,8 @@
       <c r="E25" s="32" t="n"/>
       <c r="F25" s="32" t="n"/>
       <c r="G25" s="32" t="n"/>
+      <c r="H25" s="32" t="n"/>
+      <c r="I25" s="32" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="33" t="inlineStr">
@@ -10197,6 +11727,8 @@
       <c r="E26" s="32" t="n"/>
       <c r="F26" s="32" t="n"/>
       <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
     </row>
     <row r="27" ht="14" customHeight="1"/>
     <row r="28" ht="24" customHeight="1">
@@ -10223,7 +11755,7 @@
       </c>
     </row>
     <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
           <t>SN</t>
@@ -10259,8 +11791,18 @@
           <t>Sub-group</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>Parameter Meaning</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
       <c r="A35" s="17" t="n">
         <v>1</v>
       </c>
@@ -10294,8 +11836,18 @@
           <t>10</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>Cell-level switch that enables service-request-based inter-frequency handover at bearer setup / modify.</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
       <c r="A36" s="17" t="n">
         <v>2</v>
       </c>
@@ -10329,8 +11881,18 @@
           <t>10</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>Whether the QCI is permitted to leave the serving frequency when the service is requested.</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §10.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
       <c r="A37" s="17" t="n">
         <v>3</v>
       </c>
@@ -10364,8 +11926,18 @@
           <t>10</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>Maximum time the eNodeB waits for an A4 report during gap-assisted service-request measurement.</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §10.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
       <c r="A38" s="17" t="n">
         <v>4</v>
       </c>
@@ -10399,8 +11971,18 @@
           <t>10</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated A4 RSRP threshold for service-request-based IFHO (not mixed with coverage A2).</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §10.1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
       <c r="A39" s="17" t="n">
         <v>5</v>
       </c>
@@ -10434,8 +12016,18 @@
           <t>10</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated A4 RSRQ threshold for service-request-based IFHO when RSRQ is used.</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §10.1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
       <c r="A40" s="17" t="n">
         <v>6</v>
       </c>
@@ -10469,8 +12061,18 @@
           <t>10</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>TimeToTrig for A4. 5120 ms disables service-request IFHO together with FreqPri and CQI.</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-9 / §10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
       <c r="A41" s="17" t="n">
         <v>7</v>
       </c>
@@ -10504,33 +12106,43 @@
           <t>10</t>
         </is>
       </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>When ON, after a VoLTE exception the eNodeB may set up QCI-1 if PERMIT_HO and then start IF measurement.</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §10.1.1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'00 Contents'!A1" display="Contents"/>
@@ -10539,7 +12151,7 @@
     <hyperlink ref="D4" location="'04 Basic Functions'!A1" display="Ch.4 Basic (must)"/>
   </hyperlinks>
   <pageMargins left="0.55" right="0.55" top="0.6" bottom="0.55" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LMobility Management in Connected Mode  |  Huawei eRAN21.1</oddHeader>
     <oddFooter>&amp;LMobility Management in Connected Mode Feature Parameter Description  |  10 Service-Request-based Inter-Frequency Handover&amp;RPage &amp;P of &amp;N</oddFooter>

--- a/docs/4G_LTE_Mobility_Management/Connected_Mode_eRAN21.1_Feature_Sheets.xlsx
+++ b/docs/4G_LTE_Mobility_Management/Connected_Mode_eRAN21.1_Feature_Sheets.xlsx
@@ -788,10 +788,10 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    •  Command-example dBm in the book (for example A1/A2 −85/−87 dBm, A4 −103 dBm) are not design values. They are not copied into Value.</t>
+          <t xml:space="preserve">    •  Command-example dBm in the book (for example A1/A2 −85/−87 dBm, A4 −103 dBm) are not design values. They are not copied into Value. Chapter 4 has a worked example with numbers for A1–A5 / B1 / offset clamp — those numbers are for understanding only.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
     </row>
-    <row r="16" ht="110" customHeight="1">
+    <row r="16" ht="112" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>CELLALGOSWITCH FreqPriorityHoSwitch FreqPriorIFHOSwitch = ON.
@@ -1390,7 +1390,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B18" s="29" t="n"/>
@@ -1402,14 +1402,13 @@
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="n"/>
     </row>
-    <row r="19" ht="110" customHeight="1">
+    <row r="19" ht="80" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>FreqPri A1: FreqPriInterFreqHoA1ThdRsrp / Rsrq. Trigger quantity FreqPriInterFreqHoA1TrigQuan = RSRP recommended.
-FreqPri A2 (if A2-based mode): FreqPriInterFreqHoA2ThdRsrp / Rsrq.
-Target A4: InterFreqLoadBasedHoA4ThdRsrp (+ FreqPriHoA4ThldRsrpOffset per EARFCN in later versions).
-Waiting: INTRARATHOCOMM FreqPriIFHoWaitingTimer.
-After incoming unnecessary HO: FreqPriInHoProtectionTimer &gt; 0 so the UE is not bounced back at once.</t>
+          <t>FreqPri A1: FreqPriInterFreqHoA1ThdRsrp. Example −90 dBm, Hys 2, Ms −85.  −85 − 2 = −87 &gt; −90 → serving is good, FreqPri may start (same-coverage).
+Target A4: InterFreqLoadBasedHoA4ThdRsrp + FreqPriHoA4ThldRsrpOffset. Example base −105 dBm, per-EARFCN offset +2 dB → used A4 = −103 dBm.
+Mn = −90, Hys = 2.  −92 &gt; −103 → ENTER to high band. Need not beat serving; serving can still be −85 dBm.
+Waiting: FreqPriIFHoWaitingTimer. Example 1 s. After incoming unnecessary HO: FreqPriInHoProtectionTimer example 5 s so the UE is not bounced back at once.</t>
         </is>
       </c>
       <c r="B19" s="29" t="n"/>
@@ -1437,7 +1436,7 @@
       <c r="H21" s="32" t="n"/>
       <c r="I21" s="32" t="n"/>
     </row>
-    <row r="22" ht="110" customHeight="1">
+    <row r="22" ht="96" customHeight="1">
       <c r="A22" s="33" t="inlineStr">
         <is>
           <t>HO_USE_VOIP_FREQ_ALLOWED deselected for all QCIs on the UE when VoipMeasFreqPriSwitch is ON — voice can stop FreqPri meas.
@@ -2442,7 +2441,7 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
     </row>
-    <row r="16" ht="98" customHeight="1">
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Ch.5.3 InterFreqCoverHoSwitch = ON first.
@@ -2464,7 +2463,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B18" s="29" t="n"/>
@@ -2476,11 +2475,14 @@
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="n"/>
     </row>
-    <row r="19" ht="98" customHeight="1">
+    <row r="19" ht="112" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Mobility state from HO count in a window (normal / medium / high) as in 3GPP + Huawei speed parameters.
-High-speed: prefer lower-frequency / larger-coverage target. Target still must pass coverage A3 or A4/A5.
+          <t>Mobility state from HO count in a window (normal / medium / high). Confirm the exact parameter names and window in MAE / eRAN21.1 §12.1.2.
+Example: HoNumThd = 4, HighSpeedHoNumThd = 8, SpeedStateJudgePeriod = 60 s, SpeedStateTimer = 120 s, SpeedStateValidTime = 30 s.
+If the eNodeB counts 6 intra-frequency HOs inside the 60 s judge period: 6 ≥ 4 → enter high-speed, start the 120 s timer, and after 30 s apply the high-speed parameter set.
+If the count later stays ≥ 8, keep high-speed. If it falls below 4, return to normal speed.
+High-speed: prefer lower-frequency / larger-coverage target. Target still must pass coverage A3 or A4/A5 (same numbers as Chapter 5).
 Do not set coverage A2 so low that a high-speed UE never leaves a dying small cell — speed HO is not a substitute for A2.</t>
         </is>
       </c>
@@ -2596,7 +2598,7 @@
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n"/>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="33" t="inlineStr">
         <is>
           <t>FDD. Coverage IFHO already on. Do not confuse with HighSpeedUserRedirectSwitch (railway dedicated network), which is a different option.</t>
@@ -3069,7 +3071,7 @@
       <c r="H20" s="14" t="n"/>
       <c r="I20" s="14" t="n"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>ENODEBALGOSWITCH MultiOpCtrlSwitch UtranSepOpMobilitySwitch = ON. ADD UTRANNETWORKCAPCFG with MCC, MNC, RncId and the capability bits. Prerequisite: Ch.5.4 UtranPsHoSwitch or UtranRedirectSwitch as required by the policy you want.</t>
@@ -3172,7 +3174,7 @@
       <c r="H27" s="32" t="n"/>
       <c r="I27" s="32" t="n"/>
     </row>
-    <row r="28" ht="42" customHeight="1">
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="33" t="inlineStr">
         <is>
           <t>FDD. UTRAN neighbours exist. Flash/ultra-flash/SRVCC licenses if those bits are set. Related: Ch.5.4 and CS Fallback / SRVCC documents.</t>
@@ -3786,7 +3788,7 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>MultiOpCtrlSwitch GeranSepOpMobilitySwitch = ON (confirm exact bit in MAE). Configure per-BSC GERAN capabilities. Prerequisite: Ch.5.5 GeranRedirectSwitch (and related GERAN HO switches) already match the policy you want.</t>
@@ -3889,7 +3891,7 @@
       <c r="H22" s="32" t="n"/>
       <c r="I22" s="32" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="36" customHeight="1">
       <c r="A23" s="33" t="inlineStr">
         <is>
           <t>GERAN NRT present. Related CS Fallback document for SI-by-RIM / CCO. TDD ID is TDLOFD-131210.</t>
@@ -4321,7 +4323,7 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>There is no switch in Chapter 3. Configure Chapter 4 first, then the feature chapter you need.</t>
@@ -4585,7 +4587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4750,7 +4752,7 @@
       <c r="H23" s="14" t="n"/>
       <c r="I23" s="14" t="n"/>
     </row>
-    <row r="24" ht="110" customHeight="1">
+    <row r="24" ht="80" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Neighbour frequency: FREQ_MEAS_FLAG selected. HO_TRG_FREQ_FORBID_MEAS_FLAG deselected for required HO targets.
@@ -4873,7 +4875,7 @@
       <c r="H37" s="29" t="n"/>
       <c r="I37" s="29" t="n"/>
     </row>
-    <row r="38" ht="110" customHeight="1">
+    <row r="38" ht="160" customHeight="1">
       <c r="A38" s="30" t="inlineStr">
         <is>
           <t>A1  Ms − Hys &gt; Thresh     serving becomes good (stops coverage measurement; can start FreqPri)
@@ -4884,7 +4886,7 @@
 B1  Mn + Ofn − Hys &gt; Thresh     IRAT neighbour absolutely good
 B2  Ms + Hys &lt; Th1  AND  Mn + Ofn − Hys &gt; Th2     IRAT coverage pair
 Ofn / Ofs = frequency offset. Ocn / Ocs = CellIndividualOffset (CIO). Off = A3 offset. Hys = hysteresis of that event.
-QCI/operator/SPID offsets are added to the base threshold, then clamped. Example: A3InterFreqHoA2ThdRsrp + SPID factor, then MAX(−140, MIN(−43, result)).</t>
+QCI/operator/SPID offsets are added to the base threshold, then clamped: MAX(−140, MIN(−43, result)) for RSRP.</t>
         </is>
       </c>
       <c r="B38" s="29" t="n"/>
@@ -4896,739 +4898,447 @@
       <c r="H38" s="29" t="n"/>
       <c r="I38" s="29" t="n"/>
     </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Example with values  ·  for understanding only  ·  not a live design  ·  not the book MML −85/−87/−103 dBm</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="29" t="n"/>
+      <c r="E40" s="29" t="n"/>
+      <c r="F40" s="29" t="n"/>
+      <c r="G40" s="29" t="n"/>
+      <c r="H40" s="29" t="n"/>
+      <c r="I40" s="29" t="n"/>
+    </row>
+    <row r="41" ht="128" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>One teaching set so the arithmetic is visible. Calibrate real cells from MR. Later chapters re-use the same idea.
+Assume: Ms = −95 dBm (serving RSRP), Mn = −90 dBm (neighbour RSRP), Hys = 2 dB, Ofn = Ofs = 0, Ocn = Ocs = 0, Off = 2 dB, TimeToTrig = 320 ms.
+A1  Thresh = −100 dBm.   Ms − Hys = −95 − 2 = −97.   −97 &gt; −100 → ENTER. Serving is good. Coverage measurement can stop.
+     If Ms = −105 dBm: −105 − 2 = −107.   −107 &gt; −100 → NO. A1 does not enter.
+A2  Thresh = −100 dBm.   Ms + Hys = −95 + 2 = −93.   −93 &lt; −100 → NO. Serving is not poor. Inter-frequency measurement does not start.
+     If Ms = −105 dBm: −105 + 2 = −103.   −103 &lt; −100 → ENTER. Start inter-frequency / IRAT measurement.
+TimeToTrig. The entering condition must stay true for 320 ms. If it is true for 200 ms and then Ms recovers, the timer resets and no report is sent.</t>
+        </is>
+      </c>
+      <c r="B41" s="29" t="n"/>
+      <c r="C41" s="29" t="n"/>
+      <c r="D41" s="29" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="29" t="n"/>
+      <c r="G41" s="29" t="n"/>
+      <c r="H41" s="29" t="n"/>
+      <c r="I41" s="29" t="n"/>
+    </row>
+    <row r="42" ht="6" customHeight="1"/>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Same teaching set  ·  A3 / A4 / A5  ·  still not a design</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="29" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="29" t="n"/>
+      <c r="H43" s="29" t="n"/>
+      <c r="I43" s="29" t="n"/>
+    </row>
+    <row r="44" ht="128" customHeight="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>A3  Left = Mn + Ofn + Ocn − Hys = −90 − 2 = −92.   Right = Ms + Ofs + Ocs + Off = −95 + 2 = −93.   −92 &gt; −93 → ENTER. Neighbour is relatively better.
+     If Off = 6 dB: Right = −89.   −92 &gt; −89 → NO. Larger A3 offset makes intra-frequency HO harder.
+     If CIO Ocn = +3 dB: Left = −90 + 3 − 2 = −89.   −89 &gt; −93 → still ENTER, and the neighbour looks 3 dB better.
+A4  Thresh = −105 dBm.   Mn + Ofn + Ocn − Hys = −92.   −92 &gt; −105 → ENTER. Neighbour is absolutely good enough (need not beat serving).
+     If Mn = −110 dBm: −110 − 2 = −112.   −112 &gt; −105 → NO. Target is not good enough.
+A5  Th1 = −110 dBm, Th2 = −105 dBm.   Ms + Hys = −93 &lt; −110? NO. Serving is not poor, so A5 does not enter even though the neighbour is good.
+     If Ms = −115 dBm: −115 + 2 = −113 &lt; −110 YES, and −92 &gt; −105 YES → ENTER. Serving poor AND neighbour good.</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="n"/>
+      <c r="C44" s="29" t="n"/>
+      <c r="D44" s="29" t="n"/>
+      <c r="E44" s="29" t="n"/>
+      <c r="F44" s="29" t="n"/>
+      <c r="G44" s="29" t="n"/>
+      <c r="H44" s="29" t="n"/>
+      <c r="I44" s="29" t="n"/>
+    </row>
+    <row r="45" ht="6" customHeight="1"/>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Same teaching set  ·  B1 / B2, offset clamp, A4 vs coverage A2</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="n"/>
+      <c r="C46" s="29" t="n"/>
+      <c r="D46" s="29" t="n"/>
+      <c r="E46" s="29" t="n"/>
+      <c r="F46" s="29" t="n"/>
+      <c r="G46" s="29" t="n"/>
+      <c r="H46" s="29" t="n"/>
+      <c r="I46" s="29" t="n"/>
+    </row>
+    <row r="47" ht="160" customHeight="1">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>B1  IRAT Mn = −92 (configured IRAT quantity), Ofn = 0, Hys = 2, Thresh = −100.   −92 − 2 = −94.   −94 &gt; −100 → ENTER.
+B2  Serving A2-style Th1 = −110, IRAT B1-style Th2 = −100.   Ms = −115: −115 + 2 = −113 &lt; −110 YES, and −94 &gt; −100 YES → ENTER.
+     If Ms = −95: −93 &lt; −110? NO. B2 does not enter even if the IRAT neighbour is good.
+Offset then clamp (A2 RSRP). Base A3InterFreqHoA2ThdRsrp = −100 dBm. SPID factor = +6 dB. Result = −94. MAX(−140, MIN(−43, −94)) = −94 dBm. Used A2 = −94 dBm.
+     If SPID factor = +70 dB: −100 + 70 = −30 → clamp to −43 dBm (cannot go above −43).
+     If SPID factor = −50 dB: −100 − 50 = −150 → clamp to −140 dBm (cannot go below −140).
+A4 vs coverage A2 (ping-pong). ‘A4 better than A2’ means a higher RSRP requirement: A4_thd &gt; A2_thd (for example A4 = −105, A2 = −110).
+     Safe pair: A2 = −110 dBm, A4 = −105 dBm, Mn = −102 dBm. A4: −102 − 2 = −104 &gt; −105 → HO. After HO, serving = −102. A2: −102 + 2 = −100 &lt; −110? NO. Coverage measurement does not start.
+     Unsafe pair: A2 = −100 dBm, A4 = −110 dBm, Mn = −107 dBm. A4: −107 − 2 = −109 &gt; −110 → HO. After HO, serving = −107. A2: −107 + 2 = −105 &lt; −100 YES. Coverage measurement starts at once — ping-pong.</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="29" t="n"/>
+      <c r="E47" s="29" t="n"/>
+      <c r="F47" s="29" t="n"/>
+      <c r="G47" s="29" t="n"/>
+      <c r="H47" s="29" t="n"/>
+      <c r="I47" s="29" t="n"/>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>A1/A2 Hys and TTT: InterFreqHoGroup.InterFreqHoA1A2Hyst / InterFreqHoA1A2TimeToTrig. A3 Off: IntraFreqHoA3Offset or InterFreqHoA3Offset. A4 Hys/TTT: InterFreqHoA4Hyst / InterFreqHoA4TimeToTrig.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="10" customHeight="1"/>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="21" t="inlineStr">
+    <row r="49" ht="10" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>4.1.4  Measurement objects and SMeasure</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="4" customHeight="1"/>
-    <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="51" ht="4" customHeight="1"/>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>The eNodeB filters blacklisted cells, NoHoFlag neighbours, and forbidden TA/LA. Frequencies are picked in descending priority. If the highest priority maps to several frequencies, the pick among them is random when over the object cap.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="31" t="inlineStr">
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Conditions</t>
         </is>
       </c>
-      <c r="B45" s="32" t="n"/>
-      <c r="C45" s="32" t="n"/>
-      <c r="D45" s="32" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="32" t="n"/>
-      <c r="H45" s="32" t="n"/>
-      <c r="I45" s="32" t="n"/>
-    </row>
-    <row r="46" ht="98" customHeight="1">
-      <c r="A46" s="33" t="inlineStr">
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="32" t="n"/>
+    </row>
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" s="33" t="inlineStr">
         <is>
           <t>SMeasure (HOMEASCOMM): if serving RSRP is above SMeasure, the UE may skip intra/inter/IRAT measurement. A too-high SMeasure silently kills A4.
 Measurement gap steals DL TTIs. AutoGap / gap pattern must be acceptable for VoLTE and old UEs.
 Algorithm measurement priority: voice/CSFB &gt; necessary coverage &gt; unnecessary single-UE HO &gt; ANR sampling. MEAS_OBJ_PREEMPT_SW allows a higher-priority algorithm to take the gap.</t>
         </is>
       </c>
-      <c r="B46" s="32" t="n"/>
-      <c r="C46" s="32" t="n"/>
-      <c r="D46" s="32" t="n"/>
-      <c r="E46" s="32" t="n"/>
-      <c r="F46" s="32" t="n"/>
-      <c r="G46" s="32" t="n"/>
-      <c r="H46" s="32" t="n"/>
-      <c r="I46" s="32" t="n"/>
-    </row>
-    <row r="47" ht="10" customHeight="1"/>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="B55" s="32" t="n"/>
+      <c r="C55" s="32" t="n"/>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="32" t="n"/>
+      <c r="H55" s="32" t="n"/>
+      <c r="I55" s="32" t="n"/>
+    </row>
+    <row r="56" ht="10" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>4.1.6–4.1.8  Admit, execute, punish</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="4" customHeight="1"/>
-    <row r="50" ht="44" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="58" ht="4" customHeight="1"/>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>Necessary: any QCI. Unnecessary offload: all QCIs. Prep fail is often admission or X2, not RF. Penalty timers after fail: do not treat every prep fail as an A4 problem.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="22" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Advantage</t>
         </is>
       </c>
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="B60" s="23" t="n"/>
+      <c r="C60" s="23" t="n"/>
+      <c r="D60" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Limitation</t>
         </is>
       </c>
-      <c r="E51" s="25" t="n"/>
-      <c r="F51" s="25" t="n"/>
-      <c r="G51" s="25" t="n"/>
-      <c r="H51" s="25" t="n"/>
-      <c r="I51" s="25" t="n"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="E60" s="25" t="n"/>
+      <c r="F60" s="25" t="n"/>
+      <c r="G60" s="25" t="n"/>
+      <c r="H60" s="25" t="n"/>
+      <c r="I60" s="25" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">    •  One event set serves every later feature.</t>
         </is>
       </c>
-      <c r="B52" s="23" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="27" t="inlineStr">
+      <c r="B61" s="23" t="n"/>
+      <c r="C61" s="23" t="n"/>
+      <c r="D61" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">    •  Object-cap random drop is not MLB.</t>
         </is>
       </c>
-      <c r="E52" s="25" t="n"/>
-      <c r="F52" s="25" t="n"/>
-      <c r="G52" s="25" t="n"/>
-      <c r="H52" s="25" t="n"/>
-      <c r="I52" s="25" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="E61" s="25" t="n"/>
+      <c r="F61" s="25" t="n"/>
+      <c r="G61" s="25" t="n"/>
+      <c r="H61" s="25" t="n"/>
+      <c r="I61" s="25" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">    •  QCI-specific Hys/TTT possible.</t>
         </is>
       </c>
-      <c r="B53" s="23" t="n"/>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="27" t="inlineStr">
+      <c r="B62" s="23" t="n"/>
+      <c r="C62" s="23" t="n"/>
+      <c r="D62" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">    •  RSRQ as trigger oscillates with load.</t>
         </is>
       </c>
-      <c r="E53" s="25" t="n"/>
-      <c r="F53" s="25" t="n"/>
-      <c r="G53" s="25" t="n"/>
-      <c r="H53" s="25" t="n"/>
-      <c r="I53" s="25" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="26" t="inlineStr"/>
-      <c r="B54" s="23" t="n"/>
-      <c r="C54" s="23" t="n"/>
-      <c r="D54" s="27" t="inlineStr">
+      <c r="E62" s="25" t="n"/>
+      <c r="F62" s="25" t="n"/>
+      <c r="G62" s="25" t="n"/>
+      <c r="H62" s="25" t="n"/>
+      <c r="I62" s="25" t="n"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="26" t="inlineStr"/>
+      <c r="B63" s="23" t="n"/>
+      <c r="C63" s="23" t="n"/>
+      <c r="D63" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">    •  Blind mode has higher access-failure risk.</t>
         </is>
       </c>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="25" t="n"/>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="25" t="n"/>
-      <c r="I54" s="25" t="n"/>
-    </row>
-    <row r="55" ht="14" customHeight="1"/>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="E63" s="25" t="n"/>
+      <c r="F63" s="25" t="n"/>
+      <c r="G63" s="25" t="n"/>
+      <c r="H63" s="25" t="n"/>
+      <c r="I63" s="25" t="n"/>
+    </row>
+    <row r="64" ht="14" customHeight="1"/>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Combined summary</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="6" customHeight="1"/>
-    <row r="58" ht="58" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="66" ht="6" customHeight="1"/>
+    <row r="67" ht="58" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Fix flags, NRT, object cap, SMeasure and A2 family before any dBm. RSRP trigger. A4 better than coverage A2. A4 TTT ≠ 5120 ms if Ch.6 / Ch.9 / Ch.11 inter-frequency A4 is required. Then open the feature sheet.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="14" customHeight="1"/>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
+    <row r="68" ht="14" customHeight="1"/>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>Parameter list</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="6" customHeight="1"/>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
+    <row r="70" ht="6" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>MO</t>
         </is>
       </c>
-      <c r="C62" s="16" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E71" s="16" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="F62" s="16" t="inlineStr">
+      <c r="F71" s="16" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="G71" s="16" t="inlineStr">
         <is>
           <t>Sub-group</t>
         </is>
       </c>
-      <c r="H62" s="16" t="inlineStr">
+      <c r="H71" s="16" t="inlineStr">
         <is>
           <t>Parameter Meaning</t>
         </is>
       </c>
-      <c r="I62" s="16" t="inlineStr">
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>Reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="58" customHeight="1">
-      <c r="A63" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B63" s="18" t="inlineStr">
-        <is>
-          <t>EUTRANINTERNFREQ</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>FREQ_MEAS_FLAG</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>selected</t>
-        </is>
-      </c>
-      <c r="E63" s="18" t="inlineStr">
-        <is>
-          <t>Frequency must be measured. Silent no-HO if off.</t>
-        </is>
-      </c>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G63" s="18" t="inlineStr">
-        <is>
-          <t>4.1.4</t>
-        </is>
-      </c>
-      <c r="H63" s="18" t="inlineStr">
-        <is>
-          <t>Whether the UE is configured to measure this E-UTRAN frequency in connected mode.</t>
-        </is>
-      </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="58" customHeight="1">
-      <c r="A64" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B64" s="18" t="inlineStr">
-        <is>
-          <t>EUTRANINTERNFREQ</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
-        <is>
-          <t>HO_TRG_FREQ_FORBID_MEAS_FLAG</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>deselected</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>Must be off for required HO targets.</t>
-        </is>
-      </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G64" s="18" t="inlineStr">
-        <is>
-          <t>4.1.4</t>
-        </is>
-      </c>
-      <c r="H64" s="18" t="inlineStr">
-        <is>
-          <t>If selected, this frequency is forbidden as a handover target even if measured.</t>
-        </is>
-      </c>
-      <c r="I64" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="58" customHeight="1">
-      <c r="A65" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B65" s="18" t="inlineStr">
-        <is>
-          <t>EUTRANINTERFREQNCELL</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="inlineStr">
-        <is>
-          <t>NoHoFlag</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>PERMIT_HO</t>
-        </is>
-      </c>
-      <c r="E65" s="18" t="inlineStr">
-        <is>
-          <t>Neighbour allowed as HO target.</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G65" s="18" t="inlineStr">
-        <is>
-          <t>4.1.4</t>
-        </is>
-      </c>
-      <c r="H65" s="18" t="inlineStr">
-        <is>
-          <t>Per-neighbour flag allowing or prohibiting handover to that cell.</t>
-        </is>
-      </c>
-      <c r="I65" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="58" customHeight="1">
-      <c r="A66" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B66" s="18" t="inlineStr">
-        <is>
-          <t>CELLUEMEASCONTROLCFG</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="inlineStr">
-        <is>
-          <t>MaxNonIntraMeasObjNum</t>
-        </is>
-      </c>
-      <c r="D66" s="19" t="inlineStr">
-        <is>
-          <t>≥ needed objects</t>
-        </is>
-      </c>
-      <c r="E66" s="18" t="inlineStr">
-        <is>
-          <t>Over cap: equal-priority objects drop at random.</t>
-        </is>
-      </c>
-      <c r="F66" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G66" s="18" t="inlineStr">
-        <is>
-          <t>4.1.4</t>
-        </is>
-      </c>
-      <c r="H66" s="18" t="inlineStr">
-        <is>
-          <t>Maximum number of non-intra-frequency measurement objects the eNodeB may deliver to a UE.</t>
-        </is>
-      </c>
-      <c r="I66" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="58" customHeight="1">
-      <c r="A67" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>CELLUEMEASCONTROLCFG</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="inlineStr">
-        <is>
-          <t>MaxEutranFddMeasFreqNum</t>
-        </is>
-      </c>
-      <c r="D67" s="19" t="inlineStr">
-        <is>
-          <t>≥ needed FDD freqs</t>
-        </is>
-      </c>
-      <c r="E67" s="18" t="inlineStr">
-        <is>
-          <t>Same random-drop risk for FDD.</t>
-        </is>
-      </c>
-      <c r="F67" s="17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G67" s="18" t="inlineStr">
-        <is>
-          <t>4.1.4</t>
-        </is>
-      </c>
-      <c r="H67" s="18" t="inlineStr">
-        <is>
-          <t>Maximum number of neighbouring E-UTRAN FDD frequencies that can be delivered for measurement.</t>
-        </is>
-      </c>
-      <c r="I67" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="58" customHeight="1">
-      <c r="A68" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>HOMEASCOMM</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>SMeasure</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="18" t="inlineStr">
-        <is>
-          <t>Calibrate from MR. Must not hide intended A4.</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>Tune</t>
-        </is>
-      </c>
-      <c r="G68" s="18" t="inlineStr">
-        <is>
-          <t>4.1.5</t>
-        </is>
-      </c>
-      <c r="H68" s="18" t="inlineStr">
-        <is>
-          <t>Serving-cell RSRP above this value allows the UE to skip intra/inter/IRAT measurement.</t>
-        </is>
-      </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="58" customHeight="1">
-      <c r="A69" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>INTRARATHOCOMM</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>InterFreqHoA1A2TrigQuan</t>
-        </is>
-      </c>
-      <c r="D69" s="19" t="inlineStr">
-        <is>
-          <t>RSRP</t>
-        </is>
-      </c>
-      <c r="E69" s="18" t="inlineStr">
-        <is>
-          <t>Recommended trigger quantity.</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="inlineStr">
-        <is>
-          <t>Tune</t>
-        </is>
-      </c>
-      <c r="G69" s="18" t="inlineStr">
-        <is>
-          <t>4.1.4</t>
-        </is>
-      </c>
-      <c r="H69" s="18" t="inlineStr">
-        <is>
-          <t>Quantity (RSRP / RSRQ / BOTH) used to trigger inter-frequency events A1 and A2.</t>
-        </is>
-      </c>
-      <c r="I69" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="58" customHeight="1">
-      <c r="A70" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>INTRARATHOCOMM</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>InterFreqHoA4TrigQuan</t>
-        </is>
-      </c>
-      <c r="D70" s="19" t="inlineStr">
-        <is>
-          <t>RSRP</t>
-        </is>
-      </c>
-      <c r="E70" s="18" t="inlineStr">
-        <is>
-          <t>Recommended. Reporting SAME_AS_TRIG_QUAN.</t>
-        </is>
-      </c>
-      <c r="F70" s="17" t="inlineStr">
-        <is>
-          <t>Tune</t>
-        </is>
-      </c>
-      <c r="G70" s="18" t="inlineStr">
-        <is>
-          <t>4.1.4</t>
-        </is>
-      </c>
-      <c r="H70" s="18" t="inlineStr">
-        <is>
-          <t>Quantity used to trigger inter-frequency event A4.</t>
-        </is>
-      </c>
-      <c r="I70" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="58" customHeight="1">
-      <c r="A71" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B71" s="18" t="inlineStr">
-        <is>
-          <t>INTERFREQHOGROUP</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>InterFreqHoA1A2Hyst</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="18" t="inlineStr">
-        <is>
-          <t>Hys in A1/A2 formulas. Keep A1/A2 pair consistent.</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="inlineStr">
-        <is>
-          <t>Tune</t>
-        </is>
-      </c>
-      <c r="G71" s="18" t="inlineStr">
-        <is>
-          <t>Table 4-8</t>
-        </is>
-      </c>
-      <c r="H71" s="18" t="inlineStr">
-        <is>
-          <t>Hysteresis Hys applied to entering and leaving conditions of events A1 and A2.</t>
-        </is>
-      </c>
-      <c r="I71" s="18" t="inlineStr">
-        <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
         </is>
       </c>
     </row>
     <row r="72" ht="58" customHeight="1">
       <c r="A72" s="17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>INTERFREQHOGROUP</t>
+          <t>EUTRANINTERNFREQ</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>InterFreqHoA1A2TimeToTrig</t>
+          <t>FREQ_MEAS_FLAG</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>selected</t>
         </is>
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>TTT for A1/A2. QCI-specific optional.</t>
+          <t>Frequency must be measured. Silent no-HO if off.</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>Tune</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G72" s="18" t="inlineStr">
         <is>
-          <t>Table 4-8</t>
+          <t>4.1.4</t>
         </is>
       </c>
       <c r="H72" s="18" t="inlineStr">
         <is>
-          <t>Duration TimeToTrig that A1/A2 entering or leaving condition must hold.</t>
+          <t>Whether the UE is configured to measure this E-UTRAN frequency in connected mode.</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
         </is>
       </c>
     </row>
     <row r="73" ht="58" customHeight="1">
       <c r="A73" s="17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>INTERFREQHOGROUP</t>
+          <t>EUTRANINTERNFREQ</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>InterFreqHoA4Hyst</t>
+          <t>HO_TRG_FREQ_FORBID_MEAS_FLAG</t>
         </is>
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>deselected</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>Hys in A4: Mn+Ofn+Ocn−Hys &gt; Thresh.</t>
+          <t>Must be off for required HO targets.</t>
         </is>
       </c>
       <c r="F73" s="17" t="inlineStr">
         <is>
-          <t>Tune</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>Table 4-8</t>
+          <t>4.1.4</t>
         </is>
       </c>
       <c r="H73" s="18" t="inlineStr">
         <is>
-          <t>Hysteresis Hys in the event A4 formula.</t>
+          <t>If selected, this frequency is forbidden as a handover target even if measured.</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
         </is>
       </c>
     </row>
     <row r="74" ht="58" customHeight="1">
       <c r="A74" s="17" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>INTERFREQHOGROUP</t>
+          <t>EUTRANINTERFREQNCELL</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>InterFreqHoA4TimeToTrig</t>
+          <t>NoHoFlag</t>
         </is>
       </c>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>not 5120 ms</t>
+          <t>PERMIT_HO</t>
         </is>
       </c>
       <c r="E74" s="18" t="inlineStr">
         <is>
-          <t>5120 ms disables FreqPri, CQI and service-based IFHO (eRAN21.1 Table 4-9).</t>
+          <t>Neighbour allowed as HO target.</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
@@ -5638,47 +5348,47 @@
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>Table 4-9</t>
+          <t>4.1.4</t>
         </is>
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>Duration TimeToTrig for event A4. 5120 ms is treated as disable for FreqPri / CQI / service IFHO.</t>
+          <t>Per-neighbour flag allowing or prohibiting handover to that cell.</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-9</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
         </is>
       </c>
     </row>
     <row r="75" ht="58" customHeight="1">
       <c r="A75" s="17" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>INTRAFREQHOGROUP</t>
+          <t>CELLUEMEASCONTROLCFG</t>
         </is>
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>IntraFreqHoA3Offset</t>
+          <t>MaxNonIntraMeasObjNum</t>
         </is>
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≥ needed objects</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
-          <t>Off in intra-frequency A3 formula.</t>
+          <t>Over cap: equal-priority objects drop at random.</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>Tune</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
@@ -5688,42 +5398,42 @@
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>Offset Off added on the serving side of intra-frequency event A3.</t>
+          <t>Maximum number of non-intra-frequency measurement objects the eNodeB may deliver to a UE.</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-3</t>
         </is>
       </c>
     </row>
     <row r="76" ht="58" customHeight="1">
       <c r="A76" s="17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>INTERFREQHOGROUP</t>
+          <t>CELLUEMEASCONTROLCFG</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>InterFreqHoA3Offset</t>
+          <t>MaxEutranFddMeasFreqNum</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≥ needed FDD freqs</t>
         </is>
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>Off in inter-frequency A3 formula.</t>
+          <t>Same random-drop risk for FDD.</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>Tune</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G76" s="18" t="inlineStr">
@@ -5733,27 +5443,27 @@
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>Offset Off added on the serving side of inter-frequency event A3.</t>
+          <t>Maximum number of neighbouring E-UTRAN FDD frequencies that can be delivered for measurement.</t>
         </is>
       </c>
       <c r="I76" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-3</t>
         </is>
       </c>
     </row>
     <row r="77" ht="58" customHeight="1">
       <c r="A77" s="17" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B77" s="18" t="inlineStr">
         <is>
-          <t>EUTRANINTERFREQNCELL</t>
+          <t>HOMEASCOMM</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>CellIndividualOffset</t>
+          <t>SMeasure</t>
         </is>
       </c>
       <c r="D77" s="19" t="inlineStr">
@@ -5763,7 +5473,7 @@
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>Ocn. Large CIO can mask RF overshoot.</t>
+          <t>Calibrate from MR. Must not hide intended A4.</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr">
@@ -5773,42 +5483,42 @@
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t>4.1.4</t>
+          <t>4.1.5</t>
         </is>
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>Cell-specific offset Ocn (CIO) for the neighbouring cell in A3/A4/A5.</t>
+          <t>Serving-cell RSRP above this value allows the UE to skip intra/inter/IRAT measurement.</t>
         </is>
       </c>
       <c r="I77" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.5</t>
         </is>
       </c>
     </row>
     <row r="78" ht="58" customHeight="1">
       <c r="A78" s="17" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B78" s="18" t="inlineStr">
         <is>
-          <t>EUTRANINTERNFREQ</t>
+          <t>INTRARATHOCOMM</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>QoffsetFreq</t>
+          <t>InterFreqHoA1A2TrigQuan</t>
         </is>
       </c>
       <c r="D78" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RSRP</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>Ofn / connected frequency offset.</t>
+          <t>Recommended trigger quantity.</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -5823,7 +5533,7 @@
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>Frequency-specific offset Ofn for the neighbouring frequency.</t>
+          <t>Quantity (RSRP / RSRQ / BOTH) used to trigger inter-frequency events A1 and A2.</t>
         </is>
       </c>
       <c r="I78" s="18" t="inlineStr">
@@ -5834,26 +5544,26 @@
     </row>
     <row r="79" ht="58" customHeight="1">
       <c r="A79" s="17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B79" s="18" t="inlineStr">
         <is>
-          <t>CELLHOPARACFG</t>
+          <t>INTRARATHOCOMM</t>
         </is>
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>EutranFilterCoeffRsrp</t>
+          <t>InterFreqHoA4TrigQuan</t>
         </is>
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RSRP</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>L3 RSRP filter. Over-smooth delays coverage rescue.</t>
+          <t>Recommended. Reporting SAME_AS_TRIG_QUAN.</t>
         </is>
       </c>
       <c r="F79" s="17" t="inlineStr">
@@ -5868,7 +5578,7 @@
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>Layer-3 filter coefficient applied to RSRP before event evaluation.</t>
+          <t>Quantity used to trigger inter-frequency event A4.</t>
         </is>
       </c>
       <c r="I79" s="18" t="inlineStr">
@@ -5879,26 +5589,26 @@
     </row>
     <row r="80" ht="58" customHeight="1">
       <c r="A80" s="17" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B80" s="18" t="inlineStr">
         <is>
-          <t>CELLALGOSWITCH</t>
+          <t>INTERFREQHOGROUP</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>MEAS_OBJ_PREEMPT_SW</t>
+          <t>InterFreqHoA1A2Hyst</t>
         </is>
       </c>
       <c r="D80" s="19" t="inlineStr">
         <is>
-          <t>as designed</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E80" s="18" t="inlineStr">
         <is>
-          <t>Higher-priority algorithm can take limited UE gap capability.</t>
+          <t>Hys in A1/A2 formulas. Keep A1/A2 pair consistent.</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
@@ -5908,42 +5618,42 @@
       </c>
       <c r="G80" s="18" t="inlineStr">
         <is>
-          <t>Table 4-4</t>
+          <t>Table 4-8</t>
         </is>
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>Allows a higher-priority measurement algorithm to preempt gap resources of a limited-capability UE.</t>
+          <t>Hysteresis Hys applied to entering and leaving conditions of events A1 and A2.</t>
         </is>
       </c>
       <c r="I80" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-4</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
         </is>
       </c>
     </row>
     <row r="81" ht="58" customHeight="1">
       <c r="A81" s="17" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B81" s="18" t="inlineStr">
         <is>
-          <t>ENODEBALGOSWITCH</t>
+          <t>INTERFREQHOGROUP</t>
         </is>
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>AutoGapSwitch</t>
+          <t>InterFreqHoA1A2TimeToTrig</t>
         </is>
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t>as designed</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr">
         <is>
-          <t>Gap pattern cost on DL TTI / VoLTE.</t>
+          <t>TTT for A1/A2. QCI-specific optional.</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr">
@@ -5953,113 +5663,524 @@
       </c>
       <c r="G81" s="18" t="inlineStr">
         <is>
-          <t>4.1.4</t>
+          <t>Table 4-8</t>
         </is>
       </c>
       <c r="H81" s="18" t="inlineStr">
         <is>
-          <t>Controls automatic delivery of measurement gap patterns for inter-frequency / IRAT measurement.</t>
+          <t>Duration TimeToTrig that A1/A2 entering or leaving condition must hold.</t>
         </is>
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
-          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
         </is>
       </c>
     </row>
     <row r="82" ht="58" customHeight="1">
       <c r="A82" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>INTERFREQHOGROUP</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>InterFreqHoA4Hyst</t>
+        </is>
+      </c>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>Hys in A4: Mn+Ofn+Ocn−Hys &gt; Thresh.</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>Table 4-8</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>Hysteresis Hys in the event A4 formula.</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="58" customHeight="1">
+      <c r="A83" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>INTERFREQHOGROUP</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>InterFreqHoA4TimeToTrig</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t>not 5120 ms</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>5120 ms disables FreqPri, CQI and service-based IFHO (eRAN21.1 Table 4-9).</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>Table 4-9</t>
+        </is>
+      </c>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>Duration TimeToTrig for event A4. 5120 ms is treated as disable for FreqPri / CQI / service IFHO.</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="58" customHeight="1">
+      <c r="A84" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>INTRAFREQHOGROUP</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>IntraFreqHoA3Offset</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>Off in intra-frequency A3 formula.</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>4.1.4</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>Offset Off added on the serving side of intra-frequency event A3.</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="58" customHeight="1">
+      <c r="A85" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>INTERFREQHOGROUP</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>InterFreqHoA3Offset</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>Off in inter-frequency A3 formula.</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>4.1.4</t>
+        </is>
+      </c>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>Offset Off added on the serving side of inter-frequency event A3.</t>
+        </is>
+      </c>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="58" customHeight="1">
+      <c r="A86" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>EUTRANINTERFREQNCELL</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>CellIndividualOffset</t>
+        </is>
+      </c>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>Ocn. Large CIO can mask RF overshoot.</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>4.1.4</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
+          <t>Cell-specific offset Ocn (CIO) for the neighbouring cell in A3/A4/A5.</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="58" customHeight="1">
+      <c r="A87" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>EUTRANINTERNFREQ</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>QoffsetFreq</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>Ofn / connected frequency offset.</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>4.1.4</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>Frequency-specific offset Ofn for the neighbouring frequency.</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="58" customHeight="1">
+      <c r="A88" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>CELLHOPARACFG</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>EutranFilterCoeffRsrp</t>
+        </is>
+      </c>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>L3 RSRP filter. Over-smooth delays coverage rescue.</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>4.1.4</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>Layer-3 filter coefficient applied to RSRP before event evaluation.</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="58" customHeight="1">
+      <c r="A89" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>CELLALGOSWITCH</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>MEAS_OBJ_PREEMPT_SW</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>as designed</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>Higher-priority algorithm can take limited UE gap capability.</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>Table 4-4</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>Allows a higher-priority measurement algorithm to preempt gap resources of a limited-capability UE.</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="58" customHeight="1">
+      <c r="A90" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>ENODEBALGOSWITCH</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>AutoGapSwitch</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>as designed</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>Gap pattern cost on DL TTI / VoLTE.</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>Tune</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>4.1.4</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>Controls automatic delivery of measurement gap patterns for inter-frequency / IRAT measurement.</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  §4.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="58" customHeight="1">
+      <c r="A91" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="B82" s="18" t="inlineStr">
+      <c r="B91" s="18" t="inlineStr">
         <is>
           <t>CELLQCIPARA</t>
         </is>
       </c>
-      <c r="C82" s="18" t="inlineStr">
+      <c r="C91" s="18" t="inlineStr">
         <is>
           <t>QciPriorityForHo</t>
         </is>
       </c>
-      <c r="D82" s="19" t="inlineStr">
+      <c r="D91" s="19" t="inlineStr">
         <is>
           <t>see default map</t>
         </is>
       </c>
-      <c r="E82" s="18" t="inlineStr">
+      <c r="E91" s="18" t="inlineStr">
         <is>
           <t>FDD default: QCI5=1, QCI1=2, QCI3=3, QCI2=4, QCI4=5, QCI6=6, QCI7=7, QCI8=8, QCI9=9. Smaller = higher priority.</t>
         </is>
       </c>
-      <c r="F82" s="17" t="inlineStr">
+      <c r="F91" s="17" t="inlineStr">
         <is>
           <t>Tune</t>
         </is>
       </c>
-      <c r="G82" s="18" t="inlineStr">
+      <c r="G91" s="18" t="inlineStr">
         <is>
           <t>Table 4-10</t>
         </is>
       </c>
-      <c r="H82" s="18" t="inlineStr">
+      <c r="H91" s="18" t="inlineStr">
         <is>
           <t>Priority used when several QCIs run together so the eNodeB knows which QCI’s HO parameters to deliver.</t>
         </is>
       </c>
-      <c r="I82" s="18" t="inlineStr">
+      <c r="I91" s="18" t="inlineStr">
         <is>
           <t>LBFD-002018  ·  Mobility Management in Connected Mode Feature Parameter Description  ·  eRAN21.1 Issue 08  ·  Table 4-10</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="53">
     <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A54:I54"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="D61:I61"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A21:I21"/>
-    <mergeCell ref="D53:I53"/>
+    <mergeCell ref="A57:I57"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="D62:I62"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A52:I52"/>
     <mergeCell ref="A43:I43"/>
-    <mergeCell ref="D51:I51"/>
     <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A63:C63"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="D29:I29"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D54:I54"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A67:I67"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="D60:I60"/>
     <mergeCell ref="A48:I48"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D63:I63"/>
     <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="D31:I31"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="D52:I52"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
@@ -6236,7 +6357,7 @@
       <c r="H20" s="29" t="n"/>
       <c r="I20" s="29" t="n"/>
     </row>
-    <row r="21" ht="110" customHeight="1">
+    <row r="21" ht="144" customHeight="1">
       <c r="A21" s="30" t="inlineStr">
         <is>
           <t>A3-based IFHO A2:  A3InterFreqHoA2ThdRsrp  +  operator/QCI offset (eNBCnOpQciRsvdPara)   when InterFreqHoEventType = EventA3
@@ -6244,7 +6365,9 @@
 IRAT A2:  InterRatHoA2ThdRsrp / Rsrq. Further split UTRAN vs GERAN if an A2 offset is set per RAT.
 Blind A2:  CellHoParaCfg.BlindHoA1A2ThdRsrp / Rsrq
 If measurement A2 threshold ≤ blind A2, the eNodeB delivers only blind A2.
-A4/A5 target threshold must be better than this coverage A2, or the UE ping-pongs back.</t>
+A4/A5 target threshold must be better than this coverage A2 (higher RSRP requirement: A4_thd &gt; A2_thd), or the UE ping-pongs back.
+Example (not a design): A3-based A2 base = −110 dBm, operator/QCI offset = +4 dB → −106 dBm. Clamp MAX(−140, MIN(−43, −106)) = −106 dBm. That −106 dBm is the A2 the UE uses.
+Example ping-pong check: coverage A2 = −110 dBm, so A4 must be higher than −110 dBm (for example A4 = −105 dBm). Unsafe: A2 = −100 and A4 = −110 lets a neighbour at −107 dBm HO, then A2 fires on the new cell (−107 + 2 = −105 &lt; −100).</t>
         </is>
       </c>
       <c r="B21" s="29" t="n"/>
@@ -6288,7 +6411,7 @@
       <c r="H27" s="14" t="n"/>
       <c r="I27" s="14" t="n"/>
     </row>
-    <row r="28" ht="42" customHeight="1">
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
           <t>ENODEBALGOSWITCH HoAlgoSwitch IntraFreqCoverHoSwitch = ON. IntraFreqHoA3TrigQuan = RSRP (default).</t>
@@ -6307,7 +6430,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B30" s="29" t="n"/>
@@ -6319,10 +6442,13 @@
       <c r="H30" s="29" t="n"/>
       <c r="I30" s="29" t="n"/>
     </row>
-    <row r="31" ht="42" customHeight="1">
+    <row r="31" ht="80" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>A3 enter: Mn + Ofn + Ocn − Hys &gt; Ms + Ofs + Ocs + IntraFreqHoA3Offset, true for IntraFreqHoA3TimeToTrig.</t>
+          <t>A3 enter: Mn + Ofn + Ocn − Hys &gt; Ms + Ofs + Ocs + IntraFreqHoA3Offset, true for IntraFreqHoA3TimeToTrig.
+Example: Ms = −95 dBm, Mn = −90 dBm, Hys = 2 dB, all offsets 0 except Off = 2 dB.
+Left = −90 − 2 = −92.  Right = −95 + 2 = −93.  −92 &gt; −93 → ENTER. Neighbour is 3 dB stronger, offset asks for 2 dB, hysteresis 2 dB, so A3 just passes.
+If IntraFreqHoA3Offset = 6 dB: Right = −89.  −92 &gt; −89 → NO. Increase Off to stop early intra-frequency HO.</t>
         </is>
       </c>
       <c r="B31" s="29" t="n"/>
@@ -6407,7 +6533,7 @@
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n"/>
     </row>
-    <row r="37" ht="42" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
         <is>
           <t>Chapter 4 NRT and CIO must be valid. License: none.</t>
@@ -6454,7 +6580,7 @@
       <c r="H43" s="14" t="n"/>
       <c r="I43" s="14" t="n"/>
     </row>
-    <row r="44" ht="98" customHeight="1">
+    <row r="44" ht="80" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
           <t>CELLHOPARACFG CellHoAlgoSwitch InterFreqCoverHoSwitch = ON.
@@ -6476,7 +6602,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B46" s="29" t="n"/>
@@ -6488,12 +6614,15 @@
       <c r="H46" s="29" t="n"/>
       <c r="I46" s="29" t="n"/>
     </row>
-    <row r="47" ht="84" customHeight="1">
+    <row r="47" ht="112" customHeight="1">
       <c r="A47" s="30" t="inlineStr">
         <is>
           <t>Start meas: A2  Ms + Hys &lt; A2_thd  for TTT. Stop: A1  Ms − Hys &gt; A1_thd.
 Target A3: relative. Target A4: Mn+Ofn+Ocn−Hys &gt; InterFreqHoA4ThdRSRP. Target A5: serving &lt; Th1 AND neighbour &gt; Th2.
-Preferential blind: same A2 as measurement IFHO, but HO instead of meas. Emergency blind: worse A2, policy = redirection.</t>
+Preferential blind: same A2 as measurement IFHO, but HO instead of meas. Emergency blind: worse A2, policy = redirection.
+Example A2 start: A2_thd = −110 dBm, Hys = 2 dB, Ms = −115 dBm.  −115 + 2 = −113 &lt; −110 → start inter-frequency measurement.
+Example A1 stop: A1_thd = −104 dBm (a few dB above A2 −110), Ms = −95 dBm.  −95 − 2 = −97 &gt; −104 → stop measurement, serving recovered. If Ms is still −108: −108 − 2 = −110 &gt; −104? NO — measurement continues.
+Example A4 target: A4 = −105 dBm, Mn = −90 dBm, Hys = 2.  −92 &gt; −105 → HO. Keep A4 (−105) higher than A2 (−110) so a just-good target is not immediately A2-poor.</t>
         </is>
       </c>
       <c r="B47" s="29" t="n"/>
@@ -6593,7 +6722,7 @@
       <c r="H53" s="32" t="n"/>
       <c r="I53" s="32" t="n"/>
     </row>
-    <row r="54" ht="42" customHeight="1">
+    <row r="54" ht="36" customHeight="1">
       <c r="A54" s="33" t="inlineStr">
         <is>
           <t>Ch.4 flags and object cap. A4/A5 thd better than this A2. Book MML examples −85/−87 dBm are not design values.</t>
@@ -6640,7 +6769,7 @@
       <c r="H60" s="14" t="n"/>
       <c r="I60" s="14" t="n"/>
     </row>
-    <row r="61" ht="42" customHeight="1">
+    <row r="61" ht="36" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
           <t>UtranPsHoSwitch and/or UtranRedirectSwitch = ON. InterRatHoA1A2TrigQuan = RSRP recommended.</t>
@@ -6659,7 +6788,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B63" s="29" t="n"/>
@@ -6671,10 +6800,13 @@
       <c r="H63" s="29" t="n"/>
       <c r="I63" s="29" t="n"/>
     </row>
-    <row r="64" ht="42" customHeight="1">
+    <row r="64" ht="80" customHeight="1">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>B1: Mn + Ofn − Hys &gt; B1_thd. B2: serving A2-style Th1 AND B1-style Th2.</t>
+          <t>B1: Mn + Ofn − Hys &gt; B1_thd. Example: IRAT Mn = −92, Ofn = 0, Hys = 2, B1_thd = −100.  −94 &gt; −100 → ENTER.
+B2: serving A2-style Th1 AND B1-style Th2. Example Th1 = −110, Th2 = −100, Ms = −115, Mn = −92, Hys = 2.
+     Serving: −115 + 2 = −113 &lt; −110 YES. Neighbour: −94 &gt; −100 YES → ENTER. If Ms = −95, serving −93 &lt; −110? NO — B2 does not enter.
+IRAT offload TTT must be &lt; 3 s or the 3 s meas stop kills the report.</t>
         </is>
       </c>
       <c r="B64" s="29" t="n"/>
@@ -6756,7 +6888,7 @@
       <c r="H72" s="14" t="n"/>
       <c r="I72" s="14" t="n"/>
     </row>
-    <row r="73" ht="42" customHeight="1">
+    <row r="73" ht="36" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
           <t>GeranRedirectSwitch = ON. Smaller B1 TTT toward UTRAN than GERAN makes UTRAN more likely given the same RF.</t>
@@ -6841,7 +6973,7 @@
       <c r="H81" s="14" t="n"/>
       <c r="I81" s="14" t="n"/>
     </row>
-    <row r="82" ht="42" customHeight="1">
+    <row r="82" ht="36" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
         <is>
           <t>CELLALGOSWITCH FreqLayerSwitch UtranFreqLayerMeasSwitch and/or UtranFreqLayerBlindSwitch = ON. UTRANNFREQ CsPriority / PsPriority set. Priority_0 = do not use that frequency for that service.</t>
@@ -6872,7 +7004,7 @@
       <c r="H84" s="32" t="n"/>
       <c r="I84" s="32" t="n"/>
     </row>
-    <row r="85" ht="42" customHeight="1">
+    <row r="85" ht="36" customHeight="1">
       <c r="A85" s="33" t="inlineStr">
         <is>
           <t>Needs §5.4 coverage IRAT to UTRAN. Voice vs data RAT steering: SrvccRatSteeringSwitch / PsRatSteeringSwitch. RatLayerSwitch is legacy — not recommended.</t>
@@ -8184,7 +8316,7 @@
       <c r="H18" s="32" t="n"/>
       <c r="I18" s="32" t="n"/>
     </row>
-    <row r="19" ht="110" customHeight="1">
+    <row r="19" ht="80" customHeight="1">
       <c r="A19" s="33" t="inlineStr">
         <is>
           <t>Chapter 4 object cap and A4 TTT ≠ 5120 ms.
@@ -8227,7 +8359,7 @@
       <c r="H24" s="14" t="n"/>
       <c r="I24" s="14" t="n"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
           <t>HoAlgoSwitch ServiceBasedInterFreqHoSwitch = ON  AND  CELLALGOSWITCH SrvBasedInterFreqHoSw = ON. CNOPERATORQCIPARA binds QCI to ServiceIfHoCfgGroup. InterFreqHoState = PERMIT_HO.</t>
@@ -8246,7 +8378,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B27" s="29" t="n"/>
@@ -8258,13 +8390,15 @@
       <c r="H27" s="29" t="n"/>
       <c r="I27" s="29" t="n"/>
     </row>
-    <row r="28" ht="110" customHeight="1">
+    <row r="28" ht="128" customHeight="1">
       <c r="A28" s="30" t="inlineStr">
         <is>
           <t>Target event A4. Threshold = InterFreqLoadBasedHoA4ThdRSRP + QCI/operator offset (same A4 pool as FreqPri in many versions).
 Enter: Mn + Ofn + Ocn − Hys &gt; that threshold, for InterFreqHoA4TimeToTrig.
+Example: base A4 = −105 dBm, QCI offset = +3 dB → used A4 = −102 dBm. Mn = −90, Hys = 2.  −92 &gt; −102 → ENTER.
+If coverage A2 is −110 dBm, used A4 −102 dBm is higher than A2, so the UE is not coverage-measured out of the new cell at once.
 ServiceBasedMultiFreqHoSwitch ON: for CA-incapable UEs, pick high priority + high BW + light load. CA-capable UEs are then not service-HO’d (use CA smart selection instead).
-Light load: UL-sync UE count &lt; serving MlbUeNumThd + offset, or neighbour load unknown. Neighbour must send X2 load (YES).
+Light-load example: serving MlbUeNumThd = 40, offset = 5. Neighbour UL-sync UEs = 30.  30 &lt; 40+5 → treated as light load.
 ServBasedHoBackSwitch allows return to the source frequency on the next service HO.</t>
         </is>
       </c>
@@ -8374,7 +8508,7 @@
       <c r="H37" s="14" t="n"/>
       <c r="I37" s="14" t="n"/>
     </row>
-    <row r="38" ht="42" customHeight="1">
+    <row r="38" ht="36" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
         <is>
           <t>HoAlgoSwitch UtranServiceHoSwitch = ON. SERVICEIRHOCFGGROUP InterRatHoState = MUST_HO or PERMIT_HO. Bind QCI on CNOPERATORQCIPARA.</t>
@@ -8393,7 +8527,7 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B40" s="29" t="n"/>
@@ -8405,10 +8539,11 @@
       <c r="H40" s="29" t="n"/>
       <c r="I40" s="29" t="n"/>
     </row>
-    <row r="41" ht="42" customHeight="1">
+    <row r="41" ht="48" customHeight="1">
       <c r="A41" s="30" t="inlineStr">
         <is>
-          <t>Target B1. IRAT offload TTT must be &lt; 3 s or the 3 s meas stop kills the report.</t>
+          <t>Target B1. Example: IRAT Mn = −92, Hys = 2, B1_thd = −100.  −94 &gt; −100 → ENTER.
+IRAT offload TTT must be &lt; 3 s or the 3 s meas stop kills the report.</t>
         </is>
       </c>
       <c r="B41" s="29" t="n"/>
@@ -8483,7 +8618,7 @@
       <c r="H48" s="14" t="n"/>
       <c r="I48" s="14" t="n"/>
     </row>
-    <row r="49" ht="42" customHeight="1">
+    <row r="49" ht="36" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
           <t>HoAlgoSwitch GeranServiceHoSwitch = ON. Same SERVICEIRHOCFGGROUP bind as 6.3.</t>
@@ -9344,7 +9479,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B18" s="29" t="n"/>
@@ -9356,13 +9491,15 @@
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="n"/>
     </row>
-    <row r="19" ht="98" customHeight="1">
+    <row r="19" ht="112" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Distance from TA. Precision about 100 to 150 m.
 Start: measured distance &gt; DistBasedHoThd for 10 seconds.
 Stop: measured distance ≤ stop threshold for 10 seconds.
-LTE target A4: InterFreqHoA4ThdRSRP / RSRQ (same A4 as coverage IFHO). Must still be better than coverage A2.</t>
+LTE target A4: InterFreqHoA4ThdRSRP / RSRQ (same A4 as coverage IFHO). Must still be better than coverage A2.
+Example: DistBasedHoThd = 3000 m. TA says 3200 m for 10 s → start. Then A4: Mn = −90 dBm, Hys = 2, A4 = −105 dBm.  −92 &gt; −105 → HO to the planned layer.
+If TA later falls to 2500 m for 10 s → stop distance measurement. Do not wait for coverage A2 on an overshoot lobe.</t>
         </is>
       </c>
       <c r="B19" s="29" t="n"/>
@@ -9399,7 +9536,7 @@
       <c r="H24" s="14" t="n"/>
       <c r="I24" s="14" t="n"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
           <t>CELLALGOSWITCH DistBasedHoSwitch = ON. DISTBASEDHO DistBasedMeasObjType EUTRAN = selected.</t>
@@ -9511,7 +9648,7 @@
       <c r="H34" s="14" t="n"/>
       <c r="I34" s="14" t="n"/>
     </row>
-    <row r="35" ht="42" customHeight="1">
+    <row r="35" ht="36" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
           <t>DistBasedHoSwitch = ON. DistBasedMeasObjType UTRAN-1 and/or GERAN-1. Target B1.</t>
@@ -9542,7 +9679,7 @@
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="n"/>
     </row>
-    <row r="38" ht="42" customHeight="1">
+    <row r="38" ht="36" customHeight="1">
       <c r="A38" s="33" t="inlineStr">
         <is>
           <t>Chapter 4 IRAT neighbours. Coverage IRAT is still the edge rescue; this is overshoot only.</t>
@@ -10141,7 +10278,7 @@
       <c r="H20" s="14" t="n"/>
       <c r="I20" s="14" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>ENODEBALGOSWITCH HoAlgoSwitch UlQualityInterFreqHoSwitch = ON.</t>
@@ -10160,7 +10297,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B23" s="29" t="n"/>
@@ -10172,13 +10309,15 @@
       <c r="H23" s="29" t="n"/>
       <c r="I23" s="29" t="n"/>
     </row>
-    <row r="24" ht="110" customHeight="1">
+    <row r="24" ht="128" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
           <t>Start meas:  UL MCS index &lt; UlBadQualMcsThd   AND   (actual IBLER − target IBLER) &gt; UlBadQualIblerThd
 Stop meas:  MCS ≥ MCS thd   OR   IBLER gap ≤ IBLER thd
 A4 threshold = InterFreqHoA4ThdRSRP + UlBadQualHoA4Offset   (same for RSRQ + offset)
-Blind: MCS &lt; blind MCS thd  AND  (IBLER gap − 10%) &gt; IBLER thd  AND  no A4 received.
+Example start: MCS thd = 6, IBLER thd = 5%. UE MCS = 4, actual IBLER = 12%, target IBLER = 10%.  4 &lt; 6 AND (12−10)=2% &gt; 5%?  2% &gt; 5% is NO, so measurement does not start yet (IBLER not bad enough).
+If actual IBLER = 18%: gap = 8% &gt; 5% AND MCS 4 &lt; 6 → START. Then A4: base −105 dBm + UlBadQualHoA4Offset −3 dB → used A4 = −108 dBm. Mn −90, Hys 2.  −92 &gt; −108 → HO.
+Blind: MCS &lt; blind MCS thd  AND  (IBLER gap − 10%) &gt; IBLER thd  AND  no A4 received. Example: gap 18%, thd 5%.  (18−10)=8% &gt; 5% AND still no A4 → blind redirect.
 If the QCI-1 blind switch is ON, QCI-1 may be blind-redirected; release cause to MME is always User Inactivity.</t>
         </is>
       </c>
@@ -10288,7 +10427,7 @@
       <c r="H33" s="14" t="n"/>
       <c r="I33" s="14" t="n"/>
     </row>
-    <row r="34" ht="42" customHeight="1">
+    <row r="34" ht="36" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
           <t>HoAlgoSwitch UlQualityInterRATHoSwitch = ON. Target B1 to UTRAN or GERAN.</t>
@@ -10319,7 +10458,7 @@
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="n"/>
     </row>
-    <row r="37" ht="42" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
         <is>
           <t>Chapter 4 IRAT neighbours. Same MCS/IBLER start as 8.2.</t>
@@ -10894,7 +11033,7 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
     </row>
-    <row r="16" ht="110" customHeight="1">
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Enable the CQI-based inter-frequency HO bit on CELLHOPARACFG / CELLALGOSWITCH (confirm the exact bit name in MAE on this eRAN21.1).
@@ -10916,7 +11055,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B18" s="29" t="n"/>
@@ -10928,11 +11067,13 @@
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="n"/>
     </row>
-    <row r="19" ht="84" customHeight="1">
+    <row r="19" ht="96" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Start: serving CQI stays below the CQI threshold for the configured period.
 Target A4: Mn + Ofn + Ocn − Hys &gt; A4_thd (+ any CQI-specific A4 offset if the version has one).
+Example: CQI thd = 6, UE CQI = 4 for the CQI timer → start. Serving RSRP may still be −85 dBm (coverage A2 not fired).
+Then A4 = −105 dBm, Mn = −90, Hys = 2.  −92 &gt; −105 → HO. Keep A4 better than coverage A2.
 Stop / ping-pong guard: A4_thd must be better than coverage A2 so the UE is not immediately measured out of the new cell.</t>
         </is>
       </c>
@@ -11048,7 +11189,7 @@
       <c r="H26" s="32" t="n"/>
       <c r="I26" s="32" t="n"/>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="33" t="inlineStr">
         <is>
           <t>Requires Ch.4. Does not replace Ch.5 coverage. Confirm license / bit in MAE. Do not copy book example A4 dBm into Value.</t>
@@ -11575,7 +11716,7 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
     </row>
-    <row r="16" ht="98" customHeight="1">
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>CELLALGOSWITCH HoAllowedSwitch ServiceReqInterFreqHoSwitch = ON.
@@ -11597,7 +11738,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation</t>
+          <t xml:space="preserve">  Calculation + example (not a design)</t>
         </is>
       </c>
       <c r="B18" s="29" t="n"/>
@@ -11609,12 +11750,13 @@
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="n"/>
     </row>
-    <row r="19" ht="110" customHeight="1">
+    <row r="19" ht="96" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
           <t>A4 thd = SrvReqHoA4ThdRsrp (+ SrvReqHoA4ThdRsrq if used)  — its own A4, not mixed with coverage A2.
-This A4 must still be better than coverage A2 so coverage measurement does not start immediately after arrival.
-Wait for A4: ServiceIfHoCfgGroup.A4RptWaitingTimer.
+Example: SrvReqHoA4ThdRsrp = −102 dBm, coverage A2 = −110 dBm. Used service-request A4 (−102) is higher than A2 (−110).
+Mn = −90, Hys = 2.  −92 &gt; −102 → ENTER. After HO, serving −90: −90 + 2 = −88 &lt; −110? NO, so coverage measurement does not start immediately.
+Wait for A4: ServiceIfHoCfgGroup.A4RptWaitingTimer. Example 3 s. If no A4 in 3 s, stop gap measurement so user-plane is not stalled.
 VoipExProtSwitch: if ON and VoLTE exception, set up QCI-1 if PERMIT_HO in initial context, then start IF meas after access.</t>
         </is>
       </c>
@@ -11715,7 +11857,7 @@
       <c r="H25" s="32" t="n"/>
       <c r="I25" s="32" t="n"/>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="33" t="inlineStr">
         <is>
           <t>Highest-priority QCI among configured QCIs. Serving frequency not already the target. Chapter 4 flags.</t>
